--- a/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 4_Spesialis.xlsx
+++ b/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 4_Spesialis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\titipan Feli\PROYEK GEDE\Database\Template Baru kosong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\z\TemplateJobDescBaruKosongan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA89D58D-D1D2-43EE-9FB0-B68335D1C0D5}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9148175C-3DBE-4FEC-B336-C3B4D1FB6AF4}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{B4CA32BC-DA9F-4539-8D41-F96D4CBDAEFA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>JOB DESCRIPTION</t>
   </si>
@@ -126,9 +126,6 @@
     <t>Menjalin informasi dan komunikasi dengan internal departemen</t>
   </si>
   <si>
-    <t>Berhubungan dengan seluruh departemen PT UBS perihal :</t>
-  </si>
-  <si>
     <t>Berhubungan dengan pihak eksternal dengan batasan perihal :</t>
   </si>
   <si>
@@ -187,9 +184,6 @@
     <t>InternalConnection</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Memahami alur proses keseluruhan departemen</t>
   </si>
   <si>
@@ -208,16 +202,13 @@
     <t>CodeDocument</t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
     <t>ExternalXYZConnection</t>
   </si>
   <si>
-    <t>2.</t>
+    <t>ExternalConnection</t>
   </si>
   <si>
-    <t>3.</t>
+    <t>Berhubungan dengan seluruh departemen PT XYZ perihal :</t>
   </si>
 </sst>
 </file>
@@ -636,7 +627,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -914,9 +905,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,101 +1081,110 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1668,182 +1665,182 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="170" t="s">
+      <c r="M2" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="171"/>
-      <c r="O2" s="171"/>
-      <c r="P2" s="171"/>
-      <c r="Q2" s="171"/>
-      <c r="R2" s="171"/>
-      <c r="S2" s="171"/>
-      <c r="T2" s="171"/>
-      <c r="U2" s="171"/>
-      <c r="V2" s="171"/>
-      <c r="W2" s="171"/>
-      <c r="X2" s="171"/>
-      <c r="Y2" s="171"/>
-      <c r="Z2" s="171"/>
-      <c r="AA2" s="171"/>
-      <c r="AB2" s="171"/>
-      <c r="AC2" s="171"/>
-      <c r="AD2" s="171"/>
-      <c r="AE2" s="171"/>
-      <c r="AF2" s="171"/>
-      <c r="AG2" s="171"/>
-      <c r="AH2" s="171"/>
-      <c r="AI2" s="171"/>
-      <c r="AJ2" s="171"/>
-      <c r="AK2" s="171"/>
-      <c r="AL2" s="171"/>
-      <c r="AM2" s="171"/>
-      <c r="AN2" s="171"/>
-      <c r="AO2" s="172"/>
-      <c r="AP2" s="131"/>
-      <c r="AQ2" s="132" t="s">
+      <c r="N2" s="164"/>
+      <c r="O2" s="164"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="164"/>
+      <c r="S2" s="164"/>
+      <c r="T2" s="164"/>
+      <c r="U2" s="164"/>
+      <c r="V2" s="164"/>
+      <c r="W2" s="164"/>
+      <c r="X2" s="164"/>
+      <c r="Y2" s="164"/>
+      <c r="Z2" s="164"/>
+      <c r="AA2" s="164"/>
+      <c r="AB2" s="164"/>
+      <c r="AC2" s="164"/>
+      <c r="AD2" s="164"/>
+      <c r="AE2" s="164"/>
+      <c r="AF2" s="164"/>
+      <c r="AG2" s="164"/>
+      <c r="AH2" s="164"/>
+      <c r="AI2" s="164"/>
+      <c r="AJ2" s="164"/>
+      <c r="AK2" s="164"/>
+      <c r="AL2" s="164"/>
+      <c r="AM2" s="164"/>
+      <c r="AN2" s="164"/>
+      <c r="AO2" s="165"/>
+      <c r="AP2" s="130"/>
+      <c r="AQ2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="AR2" s="132"/>
-      <c r="AS2" s="132"/>
-      <c r="AT2" s="132"/>
-      <c r="AU2" s="132"/>
-      <c r="AV2" s="133" t="s">
+      <c r="AR2" s="131"/>
+      <c r="AS2" s="131"/>
+      <c r="AT2" s="131"/>
+      <c r="AU2" s="131"/>
+      <c r="AV2" s="132" t="s">
         <v>2</v>
       </c>
-      <c r="AW2" s="133" t="s">
-        <v>40</v>
-      </c>
-      <c r="AX2" s="132"/>
-      <c r="AY2" s="132"/>
-      <c r="AZ2" s="132"/>
-      <c r="BA2" s="132"/>
-      <c r="BB2" s="132"/>
-      <c r="BC2" s="132"/>
-      <c r="BD2" s="132"/>
-      <c r="BE2" s="132"/>
-      <c r="BF2" s="132"/>
-      <c r="BG2" s="132"/>
-      <c r="BH2" s="132"/>
-      <c r="BI2" s="132"/>
-      <c r="BJ2" s="132"/>
-      <c r="BK2" s="134"/>
+      <c r="AW2" s="132" t="s">
+        <v>39</v>
+      </c>
+      <c r="AX2" s="131"/>
+      <c r="AY2" s="131"/>
+      <c r="AZ2" s="131"/>
+      <c r="BA2" s="131"/>
+      <c r="BB2" s="131"/>
+      <c r="BC2" s="131"/>
+      <c r="BD2" s="131"/>
+      <c r="BE2" s="131"/>
+      <c r="BF2" s="131"/>
+      <c r="BG2" s="131"/>
+      <c r="BH2" s="131"/>
+      <c r="BI2" s="131"/>
+      <c r="BJ2" s="131"/>
+      <c r="BK2" s="133"/>
       <c r="BL2" s="6"/>
     </row>
     <row r="3" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-      <c r="P3" s="174"/>
-      <c r="Q3" s="174"/>
-      <c r="R3" s="174"/>
-      <c r="S3" s="174"/>
-      <c r="T3" s="174"/>
-      <c r="U3" s="174"/>
-      <c r="V3" s="174"/>
-      <c r="W3" s="174"/>
-      <c r="X3" s="174"/>
-      <c r="Y3" s="174"/>
-      <c r="Z3" s="174"/>
-      <c r="AA3" s="174"/>
-      <c r="AB3" s="174"/>
-      <c r="AC3" s="174"/>
-      <c r="AD3" s="174"/>
-      <c r="AE3" s="174"/>
-      <c r="AF3" s="174"/>
-      <c r="AG3" s="174"/>
-      <c r="AH3" s="174"/>
-      <c r="AI3" s="174"/>
-      <c r="AJ3" s="174"/>
-      <c r="AK3" s="174"/>
-      <c r="AL3" s="174"/>
-      <c r="AM3" s="174"/>
-      <c r="AN3" s="174"/>
-      <c r="AO3" s="175"/>
-      <c r="AP3" s="135"/>
-      <c r="AQ3" s="136"/>
-      <c r="AR3" s="136"/>
-      <c r="AS3" s="136"/>
-      <c r="AT3" s="136"/>
-      <c r="AU3" s="136"/>
-      <c r="AV3" s="137"/>
-      <c r="AW3" s="137"/>
-      <c r="AX3" s="136"/>
-      <c r="AY3" s="136"/>
-      <c r="AZ3" s="136"/>
-      <c r="BA3" s="136"/>
-      <c r="BB3" s="136"/>
-      <c r="BC3" s="136"/>
-      <c r="BD3" s="136"/>
-      <c r="BE3" s="136"/>
-      <c r="BF3" s="136"/>
-      <c r="BG3" s="136"/>
-      <c r="BH3" s="136"/>
-      <c r="BI3" s="136"/>
-      <c r="BJ3" s="136"/>
-      <c r="BK3" s="138"/>
+      <c r="M3" s="166"/>
+      <c r="N3" s="167"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="167"/>
+      <c r="Q3" s="167"/>
+      <c r="R3" s="167"/>
+      <c r="S3" s="167"/>
+      <c r="T3" s="167"/>
+      <c r="U3" s="167"/>
+      <c r="V3" s="167"/>
+      <c r="W3" s="167"/>
+      <c r="X3" s="167"/>
+      <c r="Y3" s="167"/>
+      <c r="Z3" s="167"/>
+      <c r="AA3" s="167"/>
+      <c r="AB3" s="167"/>
+      <c r="AC3" s="167"/>
+      <c r="AD3" s="167"/>
+      <c r="AE3" s="167"/>
+      <c r="AF3" s="167"/>
+      <c r="AG3" s="167"/>
+      <c r="AH3" s="167"/>
+      <c r="AI3" s="167"/>
+      <c r="AJ3" s="167"/>
+      <c r="AK3" s="167"/>
+      <c r="AL3" s="167"/>
+      <c r="AM3" s="167"/>
+      <c r="AN3" s="167"/>
+      <c r="AO3" s="168"/>
+      <c r="AP3" s="134"/>
+      <c r="AQ3" s="135"/>
+      <c r="AR3" s="135"/>
+      <c r="AS3" s="135"/>
+      <c r="AT3" s="135"/>
+      <c r="AU3" s="135"/>
+      <c r="AV3" s="136"/>
+      <c r="AW3" s="136"/>
+      <c r="AX3" s="135"/>
+      <c r="AY3" s="135"/>
+      <c r="AZ3" s="135"/>
+      <c r="BA3" s="135"/>
+      <c r="BB3" s="135"/>
+      <c r="BC3" s="135"/>
+      <c r="BD3" s="135"/>
+      <c r="BE3" s="135"/>
+      <c r="BF3" s="135"/>
+      <c r="BG3" s="135"/>
+      <c r="BH3" s="135"/>
+      <c r="BI3" s="135"/>
+      <c r="BJ3" s="135"/>
+      <c r="BK3" s="137"/>
     </row>
     <row r="4" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-      <c r="P4" s="174"/>
-      <c r="Q4" s="174"/>
-      <c r="R4" s="174"/>
-      <c r="S4" s="174"/>
-      <c r="T4" s="174"/>
-      <c r="U4" s="174"/>
-      <c r="V4" s="174"/>
-      <c r="W4" s="174"/>
-      <c r="X4" s="174"/>
-      <c r="Y4" s="174"/>
-      <c r="Z4" s="174"/>
-      <c r="AA4" s="174"/>
-      <c r="AB4" s="174"/>
-      <c r="AC4" s="174"/>
-      <c r="AD4" s="174"/>
-      <c r="AE4" s="174"/>
-      <c r="AF4" s="174"/>
-      <c r="AG4" s="174"/>
-      <c r="AH4" s="174"/>
-      <c r="AI4" s="174"/>
-      <c r="AJ4" s="174"/>
-      <c r="AK4" s="174"/>
-      <c r="AL4" s="174"/>
-      <c r="AM4" s="174"/>
-      <c r="AN4" s="174"/>
-      <c r="AO4" s="175"/>
-      <c r="AP4" s="135"/>
-      <c r="AQ4" s="136" t="s">
+      <c r="M4" s="166"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="167"/>
+      <c r="W4" s="167"/>
+      <c r="X4" s="167"/>
+      <c r="Y4" s="167"/>
+      <c r="Z4" s="167"/>
+      <c r="AA4" s="167"/>
+      <c r="AB4" s="167"/>
+      <c r="AC4" s="167"/>
+      <c r="AD4" s="167"/>
+      <c r="AE4" s="167"/>
+      <c r="AF4" s="167"/>
+      <c r="AG4" s="167"/>
+      <c r="AH4" s="167"/>
+      <c r="AI4" s="167"/>
+      <c r="AJ4" s="167"/>
+      <c r="AK4" s="167"/>
+      <c r="AL4" s="167"/>
+      <c r="AM4" s="167"/>
+      <c r="AN4" s="167"/>
+      <c r="AO4" s="168"/>
+      <c r="AP4" s="134"/>
+      <c r="AQ4" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="AR4" s="136"/>
-      <c r="AS4" s="136"/>
-      <c r="AT4" s="136"/>
-      <c r="AU4" s="136"/>
-      <c r="AV4" s="137" t="s">
+      <c r="AR4" s="135"/>
+      <c r="AS4" s="135"/>
+      <c r="AT4" s="135"/>
+      <c r="AU4" s="135"/>
+      <c r="AV4" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="AW4" s="137" t="s">
-        <v>41</v>
-      </c>
-      <c r="AX4" s="136"/>
-      <c r="AY4" s="136"/>
-      <c r="AZ4" s="136"/>
-      <c r="BA4" s="136"/>
-      <c r="BB4" s="136"/>
-      <c r="BC4" s="136"/>
-      <c r="BD4" s="136"/>
-      <c r="BE4" s="136"/>
-      <c r="BF4" s="136"/>
-      <c r="BG4" s="136"/>
-      <c r="BH4" s="136"/>
-      <c r="BI4" s="136"/>
-      <c r="BJ4" s="136"/>
-      <c r="BK4" s="138"/>
+      <c r="AW4" s="136" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX4" s="135"/>
+      <c r="AY4" s="135"/>
+      <c r="AZ4" s="135"/>
+      <c r="BA4" s="135"/>
+      <c r="BB4" s="135"/>
+      <c r="BC4" s="135"/>
+      <c r="BD4" s="135"/>
+      <c r="BE4" s="135"/>
+      <c r="BF4" s="135"/>
+      <c r="BG4" s="135"/>
+      <c r="BH4" s="135"/>
+      <c r="BI4" s="135"/>
+      <c r="BJ4" s="135"/>
+      <c r="BK4" s="137"/>
       <c r="BL4" s="9"/>
     </row>
     <row r="5" spans="2:68" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1858,63 +1855,63 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="177"/>
-      <c r="O5" s="177"/>
-      <c r="P5" s="177"/>
-      <c r="Q5" s="177"/>
-      <c r="R5" s="177"/>
-      <c r="S5" s="177"/>
-      <c r="T5" s="177"/>
-      <c r="U5" s="177"/>
-      <c r="V5" s="177"/>
-      <c r="W5" s="177"/>
-      <c r="X5" s="177"/>
-      <c r="Y5" s="177"/>
-      <c r="Z5" s="177"/>
-      <c r="AA5" s="177"/>
-      <c r="AB5" s="177"/>
-      <c r="AC5" s="177"/>
-      <c r="AD5" s="177"/>
-      <c r="AE5" s="177"/>
-      <c r="AF5" s="177"/>
-      <c r="AG5" s="177"/>
-      <c r="AH5" s="177"/>
-      <c r="AI5" s="177"/>
-      <c r="AJ5" s="177"/>
-      <c r="AK5" s="177"/>
-      <c r="AL5" s="177"/>
-      <c r="AM5" s="177"/>
-      <c r="AN5" s="177"/>
-      <c r="AO5" s="178"/>
-      <c r="AP5" s="139"/>
-      <c r="AQ5" s="140" t="s">
+      <c r="M5" s="169"/>
+      <c r="N5" s="170"/>
+      <c r="O5" s="170"/>
+      <c r="P5" s="170"/>
+      <c r="Q5" s="170"/>
+      <c r="R5" s="170"/>
+      <c r="S5" s="170"/>
+      <c r="T5" s="170"/>
+      <c r="U5" s="170"/>
+      <c r="V5" s="170"/>
+      <c r="W5" s="170"/>
+      <c r="X5" s="170"/>
+      <c r="Y5" s="170"/>
+      <c r="Z5" s="170"/>
+      <c r="AA5" s="170"/>
+      <c r="AB5" s="170"/>
+      <c r="AC5" s="170"/>
+      <c r="AD5" s="170"/>
+      <c r="AE5" s="170"/>
+      <c r="AF5" s="170"/>
+      <c r="AG5" s="170"/>
+      <c r="AH5" s="170"/>
+      <c r="AI5" s="170"/>
+      <c r="AJ5" s="170"/>
+      <c r="AK5" s="170"/>
+      <c r="AL5" s="170"/>
+      <c r="AM5" s="170"/>
+      <c r="AN5" s="170"/>
+      <c r="AO5" s="171"/>
+      <c r="AP5" s="138"/>
+      <c r="AQ5" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="AR5" s="140"/>
-      <c r="AS5" s="140"/>
-      <c r="AT5" s="140"/>
-      <c r="AU5" s="140"/>
-      <c r="AV5" s="110" t="s">
+      <c r="AR5" s="139"/>
+      <c r="AS5" s="139"/>
+      <c r="AT5" s="139"/>
+      <c r="AU5" s="139"/>
+      <c r="AV5" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="AW5" s="110" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX5" s="140"/>
-      <c r="AY5" s="140"/>
-      <c r="AZ5" s="140"/>
-      <c r="BA5" s="140"/>
-      <c r="BB5" s="140"/>
-      <c r="BC5" s="140"/>
-      <c r="BD5" s="140"/>
-      <c r="BE5" s="140"/>
-      <c r="BF5" s="140"/>
-      <c r="BG5" s="140"/>
-      <c r="BH5" s="140"/>
-      <c r="BI5" s="140"/>
-      <c r="BJ5" s="140"/>
-      <c r="BK5" s="141"/>
+      <c r="AW5" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="AX5" s="139"/>
+      <c r="AY5" s="139"/>
+      <c r="AZ5" s="139"/>
+      <c r="BA5" s="139"/>
+      <c r="BB5" s="139"/>
+      <c r="BC5" s="139"/>
+      <c r="BD5" s="139"/>
+      <c r="BE5" s="139"/>
+      <c r="BF5" s="139"/>
+      <c r="BG5" s="139"/>
+      <c r="BH5" s="139"/>
+      <c r="BI5" s="139"/>
+      <c r="BJ5" s="139"/>
+      <c r="BK5" s="140"/>
       <c r="BL5" s="13"/>
     </row>
     <row r="6" spans="2:68" ht="6.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2049,99 +2046,99 @@
       <c r="BP7" s="22"/>
     </row>
     <row r="8" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="161" t="s">
+      <c r="B8" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="162"/>
-      <c r="D8" s="162"/>
-      <c r="E8" s="162"/>
-      <c r="F8" s="162"/>
-      <c r="G8" s="162"/>
-      <c r="H8" s="162"/>
-      <c r="I8" s="162"/>
-      <c r="J8" s="162"/>
-      <c r="K8" s="162"/>
-      <c r="L8" s="162"/>
-      <c r="M8" s="162"/>
-      <c r="N8" s="162"/>
-      <c r="O8" s="162"/>
-      <c r="P8" s="162"/>
-      <c r="Q8" s="162"/>
-      <c r="R8" s="162"/>
-      <c r="S8" s="162"/>
-      <c r="T8" s="162"/>
-      <c r="U8" s="162"/>
-      <c r="V8" s="162"/>
-      <c r="W8" s="163"/>
-      <c r="X8" s="161" t="s">
+      <c r="C8" s="173"/>
+      <c r="D8" s="173"/>
+      <c r="E8" s="173"/>
+      <c r="F8" s="173"/>
+      <c r="G8" s="173"/>
+      <c r="H8" s="173"/>
+      <c r="I8" s="173"/>
+      <c r="J8" s="173"/>
+      <c r="K8" s="173"/>
+      <c r="L8" s="173"/>
+      <c r="M8" s="173"/>
+      <c r="N8" s="173"/>
+      <c r="O8" s="173"/>
+      <c r="P8" s="173"/>
+      <c r="Q8" s="173"/>
+      <c r="R8" s="173"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="173"/>
+      <c r="U8" s="173"/>
+      <c r="V8" s="173"/>
+      <c r="W8" s="174"/>
+      <c r="X8" s="172" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="162"/>
-      <c r="Z8" s="162"/>
-      <c r="AA8" s="162"/>
-      <c r="AB8" s="162"/>
-      <c r="AC8" s="162"/>
-      <c r="AD8" s="162"/>
-      <c r="AE8" s="162"/>
-      <c r="AF8" s="162"/>
-      <c r="AG8" s="162"/>
-      <c r="AH8" s="162"/>
-      <c r="AI8" s="162"/>
-      <c r="AJ8" s="162"/>
-      <c r="AK8" s="162"/>
-      <c r="AL8" s="162"/>
-      <c r="AM8" s="162"/>
-      <c r="AN8" s="162"/>
-      <c r="AO8" s="163"/>
+      <c r="Y8" s="173"/>
+      <c r="Z8" s="173"/>
+      <c r="AA8" s="173"/>
+      <c r="AB8" s="173"/>
+      <c r="AC8" s="173"/>
+      <c r="AD8" s="173"/>
+      <c r="AE8" s="173"/>
+      <c r="AF8" s="173"/>
+      <c r="AG8" s="173"/>
+      <c r="AH8" s="173"/>
+      <c r="AI8" s="173"/>
+      <c r="AJ8" s="173"/>
+      <c r="AK8" s="173"/>
+      <c r="AL8" s="173"/>
+      <c r="AM8" s="173"/>
+      <c r="AN8" s="173"/>
+      <c r="AO8" s="174"/>
       <c r="AP8" s="24"/>
-      <c r="AQ8" s="161" t="s">
+      <c r="AQ8" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="AR8" s="162"/>
-      <c r="AS8" s="162"/>
-      <c r="AT8" s="162"/>
-      <c r="AU8" s="162"/>
-      <c r="AV8" s="162"/>
-      <c r="AW8" s="162"/>
-      <c r="AX8" s="162"/>
-      <c r="AY8" s="162"/>
-      <c r="AZ8" s="162"/>
-      <c r="BA8" s="162"/>
-      <c r="BB8" s="162"/>
-      <c r="BC8" s="162"/>
-      <c r="BD8" s="162"/>
-      <c r="BE8" s="162"/>
-      <c r="BF8" s="162"/>
-      <c r="BG8" s="162"/>
-      <c r="BH8" s="162"/>
-      <c r="BI8" s="162"/>
-      <c r="BJ8" s="162"/>
-      <c r="BK8" s="163"/>
+      <c r="AR8" s="173"/>
+      <c r="AS8" s="173"/>
+      <c r="AT8" s="173"/>
+      <c r="AU8" s="173"/>
+      <c r="AV8" s="173"/>
+      <c r="AW8" s="173"/>
+      <c r="AX8" s="173"/>
+      <c r="AY8" s="173"/>
+      <c r="AZ8" s="173"/>
+      <c r="BA8" s="173"/>
+      <c r="BB8" s="173"/>
+      <c r="BC8" s="173"/>
+      <c r="BD8" s="173"/>
+      <c r="BE8" s="173"/>
+      <c r="BF8" s="173"/>
+      <c r="BG8" s="173"/>
+      <c r="BH8" s="173"/>
+      <c r="BI8" s="173"/>
+      <c r="BJ8" s="173"/>
+      <c r="BK8" s="174"/>
       <c r="BL8" s="1"/>
       <c r="BN8" s="22"/>
     </row>
     <row r="9" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
-      <c r="X9" s="179" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y9" s="180"/>
-      <c r="Z9" s="180"/>
-      <c r="AA9" s="180"/>
-      <c r="AB9" s="180"/>
-      <c r="AC9" s="180"/>
-      <c r="AD9" s="180"/>
-      <c r="AE9" s="180"/>
-      <c r="AF9" s="180"/>
-      <c r="AG9" s="180"/>
-      <c r="AH9" s="180"/>
-      <c r="AI9" s="180"/>
-      <c r="AJ9" s="180"/>
-      <c r="AK9" s="180"/>
-      <c r="AL9" s="180"/>
-      <c r="AM9" s="180"/>
-      <c r="AN9" s="180"/>
-      <c r="AO9" s="181"/>
+      <c r="X9" s="175" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" s="176"/>
+      <c r="Z9" s="176"/>
+      <c r="AA9" s="176"/>
+      <c r="AB9" s="176"/>
+      <c r="AC9" s="176"/>
+      <c r="AD9" s="176"/>
+      <c r="AE9" s="176"/>
+      <c r="AF9" s="176"/>
+      <c r="AG9" s="176"/>
+      <c r="AH9" s="176"/>
+      <c r="AI9" s="176"/>
+      <c r="AJ9" s="176"/>
+      <c r="AK9" s="176"/>
+      <c r="AL9" s="176"/>
+      <c r="AM9" s="176"/>
+      <c r="AN9" s="176"/>
+      <c r="AO9" s="177"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="25" t="s">
         <v>8</v>
@@ -2152,24 +2149,24 @@
     </row>
     <row r="10" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7"/>
-      <c r="X10" s="182"/>
-      <c r="Y10" s="183"/>
-      <c r="Z10" s="183"/>
-      <c r="AA10" s="183"/>
-      <c r="AB10" s="183"/>
-      <c r="AC10" s="183"/>
-      <c r="AD10" s="183"/>
-      <c r="AE10" s="183"/>
-      <c r="AF10" s="183"/>
-      <c r="AG10" s="183"/>
-      <c r="AH10" s="183"/>
-      <c r="AI10" s="183"/>
-      <c r="AJ10" s="183"/>
-      <c r="AK10" s="183"/>
-      <c r="AL10" s="183"/>
-      <c r="AM10" s="183"/>
-      <c r="AN10" s="183"/>
-      <c r="AO10" s="184"/>
+      <c r="X10" s="178"/>
+      <c r="Y10" s="179"/>
+      <c r="Z10" s="179"/>
+      <c r="AA10" s="179"/>
+      <c r="AB10" s="179"/>
+      <c r="AC10" s="179"/>
+      <c r="AD10" s="179"/>
+      <c r="AE10" s="179"/>
+      <c r="AF10" s="179"/>
+      <c r="AG10" s="179"/>
+      <c r="AH10" s="179"/>
+      <c r="AI10" s="179"/>
+      <c r="AJ10" s="179"/>
+      <c r="AK10" s="179"/>
+      <c r="AL10" s="179"/>
+      <c r="AM10" s="179"/>
+      <c r="AN10" s="179"/>
+      <c r="AO10" s="180"/>
       <c r="AP10" s="26"/>
       <c r="AQ10" s="33"/>
       <c r="AR10" s="50"/>
@@ -2195,24 +2192,24 @@
     <row r="11" spans="2:68" ht="16.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="W11" s="8"/>
-      <c r="X11" s="185"/>
-      <c r="Y11" s="186"/>
-      <c r="Z11" s="186"/>
-      <c r="AA11" s="186"/>
-      <c r="AB11" s="186"/>
-      <c r="AC11" s="186"/>
-      <c r="AD11" s="186"/>
-      <c r="AE11" s="186"/>
-      <c r="AF11" s="186"/>
-      <c r="AG11" s="186"/>
-      <c r="AH11" s="186"/>
-      <c r="AI11" s="186"/>
-      <c r="AJ11" s="186"/>
-      <c r="AK11" s="186"/>
-      <c r="AL11" s="186"/>
-      <c r="AM11" s="186"/>
-      <c r="AN11" s="186"/>
-      <c r="AO11" s="187"/>
+      <c r="X11" s="181"/>
+      <c r="Y11" s="182"/>
+      <c r="Z11" s="182"/>
+      <c r="AA11" s="182"/>
+      <c r="AB11" s="182"/>
+      <c r="AC11" s="182"/>
+      <c r="AD11" s="182"/>
+      <c r="AE11" s="182"/>
+      <c r="AF11" s="182"/>
+      <c r="AG11" s="182"/>
+      <c r="AH11" s="182"/>
+      <c r="AI11" s="182"/>
+      <c r="AJ11" s="182"/>
+      <c r="AK11" s="182"/>
+      <c r="AL11" s="182"/>
+      <c r="AM11" s="182"/>
+      <c r="AN11" s="182"/>
+      <c r="AO11" s="183"/>
       <c r="AP11" s="26"/>
       <c r="AQ11" s="57"/>
       <c r="AR11" s="56"/>
@@ -2239,36 +2236,36 @@
     <row r="12" spans="2:68" ht="16.7" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="W12" s="8"/>
-      <c r="X12" s="161" t="s">
+      <c r="X12" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="162"/>
-      <c r="Z12" s="162"/>
-      <c r="AA12" s="162"/>
-      <c r="AB12" s="162"/>
-      <c r="AC12" s="162"/>
-      <c r="AD12" s="162"/>
-      <c r="AE12" s="162"/>
-      <c r="AF12" s="162"/>
-      <c r="AG12" s="162"/>
-      <c r="AH12" s="162"/>
-      <c r="AI12" s="162"/>
-      <c r="AJ12" s="162"/>
-      <c r="AK12" s="162"/>
-      <c r="AL12" s="162"/>
-      <c r="AM12" s="162"/>
-      <c r="AN12" s="162"/>
-      <c r="AO12" s="163"/>
+      <c r="Y12" s="173"/>
+      <c r="Z12" s="173"/>
+      <c r="AA12" s="173"/>
+      <c r="AB12" s="173"/>
+      <c r="AC12" s="173"/>
+      <c r="AD12" s="173"/>
+      <c r="AE12" s="173"/>
+      <c r="AF12" s="173"/>
+      <c r="AG12" s="173"/>
+      <c r="AH12" s="173"/>
+      <c r="AI12" s="173"/>
+      <c r="AJ12" s="173"/>
+      <c r="AK12" s="173"/>
+      <c r="AL12" s="173"/>
+      <c r="AM12" s="173"/>
+      <c r="AN12" s="173"/>
+      <c r="AO12" s="174"/>
       <c r="AP12" s="26"/>
-      <c r="AQ12" s="113" t="s">
+      <c r="AQ12" s="112" t="s">
         <v>10</v>
       </c>
       <c r="AR12" s="50"/>
       <c r="AS12" s="50"/>
       <c r="AT12" s="50"/>
-      <c r="AU12" s="113"/>
-      <c r="AV12" s="113"/>
-      <c r="AW12" s="114"/>
+      <c r="AU12" s="112"/>
+      <c r="AV12" s="112"/>
+      <c r="AW12" s="113"/>
       <c r="AX12" s="56"/>
       <c r="AY12" s="56"/>
       <c r="AZ12" s="56"/>
@@ -2285,34 +2282,34 @@
     </row>
     <row r="13" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
-      <c r="X13" s="112"/>
+      <c r="X13" s="111"/>
       <c r="Y13" s="31"/>
       <c r="AP13" s="32"/>
       <c r="AQ13" s="33"/>
-      <c r="AR13" s="113"/>
-      <c r="AS13" s="113"/>
-      <c r="AT13" s="113"/>
-      <c r="AU13" s="113"/>
-      <c r="AV13" s="113"/>
-      <c r="AW13" s="113"/>
-      <c r="AX13" s="113"/>
-      <c r="AY13" s="113"/>
-      <c r="AZ13" s="113"/>
-      <c r="BA13" s="113"/>
-      <c r="BB13" s="113"/>
-      <c r="BC13" s="113"/>
-      <c r="BD13" s="113"/>
-      <c r="BE13" s="113"/>
-      <c r="BF13" s="113"/>
-      <c r="BG13" s="113"/>
-      <c r="BH13" s="113"/>
-      <c r="BI13" s="113"/>
+      <c r="AR13" s="112"/>
+      <c r="AS13" s="112"/>
+      <c r="AT13" s="112"/>
+      <c r="AU13" s="112"/>
+      <c r="AV13" s="112"/>
+      <c r="AW13" s="112"/>
+      <c r="AX13" s="112"/>
+      <c r="AY13" s="112"/>
+      <c r="AZ13" s="112"/>
+      <c r="BA13" s="112"/>
+      <c r="BB13" s="112"/>
+      <c r="BC13" s="112"/>
+      <c r="BD13" s="112"/>
+      <c r="BE13" s="112"/>
+      <c r="BF13" s="112"/>
+      <c r="BG13" s="112"/>
+      <c r="BH13" s="112"/>
+      <c r="BI13" s="112"/>
       <c r="BJ13" s="1"/>
       <c r="BK13" s="34"/>
     </row>
     <row r="14" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="7"/>
-      <c r="X14" s="112"/>
+      <c r="X14" s="111"/>
       <c r="Y14" s="35"/>
       <c r="Z14" s="22"/>
       <c r="AO14" s="8"/>
@@ -2321,9 +2318,9 @@
       <c r="AR14" s="56"/>
       <c r="AS14" s="56"/>
       <c r="AT14" s="56"/>
-      <c r="AU14" s="113"/>
-      <c r="AV14" s="113"/>
-      <c r="AW14" s="115"/>
+      <c r="AU14" s="112"/>
+      <c r="AV14" s="112"/>
+      <c r="AW14" s="114"/>
       <c r="AX14" s="56"/>
       <c r="AY14" s="56"/>
       <c r="AZ14" s="56"/>
@@ -2341,7 +2338,7 @@
     </row>
     <row r="15" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="7"/>
-      <c r="X15" s="111"/>
+      <c r="X15" s="110"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="22"/>
       <c r="AA15" s="22"/>
@@ -2360,15 +2357,15 @@
       <c r="AN15" s="22"/>
       <c r="AO15" s="22"/>
       <c r="AP15" s="26"/>
-      <c r="AQ15" s="113" t="s">
-        <v>39</v>
+      <c r="AQ15" s="112" t="s">
+        <v>38</v>
       </c>
       <c r="AR15" s="50"/>
       <c r="AS15" s="50"/>
       <c r="AT15" s="50"/>
-      <c r="AU15" s="113"/>
-      <c r="AV15" s="113"/>
-      <c r="AW15" s="116"/>
+      <c r="AU15" s="112"/>
+      <c r="AV15" s="112"/>
+      <c r="AW15" s="115"/>
       <c r="AX15" s="56"/>
       <c r="AY15" s="56"/>
       <c r="AZ15" s="56"/>
@@ -2386,7 +2383,7 @@
     <row r="16" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="W16" s="8"/>
-      <c r="X16" s="111"/>
+      <c r="X16" s="110"/>
       <c r="Y16" s="31"/>
       <c r="Z16" s="22"/>
       <c r="AA16" s="22"/>
@@ -2409,9 +2406,9 @@
       <c r="AR16" s="50"/>
       <c r="AS16" s="50"/>
       <c r="AT16" s="50"/>
-      <c r="AU16" s="113"/>
-      <c r="AV16" s="113"/>
-      <c r="AW16" s="116"/>
+      <c r="AU16" s="112"/>
+      <c r="AV16" s="112"/>
+      <c r="AW16" s="115"/>
       <c r="AX16" s="56"/>
       <c r="AY16" s="56"/>
       <c r="AZ16" s="56"/>
@@ -2648,19 +2645,19 @@
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
-      <c r="M22" s="110" t="s">
-        <v>51</v>
-      </c>
-      <c r="N22" s="110"/>
-      <c r="O22" s="110"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="110" t="s">
-        <v>52</v>
-      </c>
-      <c r="S22" s="110"/>
-      <c r="T22" s="110"/>
-      <c r="U22" s="110"/>
+      <c r="M22" s="109" t="s">
+        <v>49</v>
+      </c>
+      <c r="N22" s="109"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="109" t="s">
+        <v>50</v>
+      </c>
+      <c r="S22" s="109"/>
+      <c r="T22" s="109"/>
+      <c r="U22" s="109"/>
       <c r="V22" s="11"/>
       <c r="W22" s="12"/>
       <c r="X22" s="39"/>
@@ -2706,77 +2703,77 @@
       <c r="BN22" s="22"/>
     </row>
     <row r="23" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="161" t="s">
+      <c r="B23" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="162"/>
-      <c r="D23" s="162"/>
-      <c r="E23" s="162"/>
-      <c r="F23" s="162"/>
-      <c r="G23" s="162"/>
-      <c r="H23" s="162"/>
-      <c r="I23" s="162"/>
-      <c r="J23" s="162"/>
-      <c r="K23" s="162"/>
-      <c r="L23" s="162"/>
-      <c r="M23" s="162"/>
-      <c r="N23" s="162"/>
-      <c r="O23" s="162"/>
-      <c r="P23" s="162"/>
-      <c r="Q23" s="162"/>
-      <c r="R23" s="162"/>
-      <c r="S23" s="162"/>
-      <c r="T23" s="162"/>
-      <c r="U23" s="162"/>
-      <c r="V23" s="162"/>
-      <c r="W23" s="162"/>
-      <c r="X23" s="162"/>
-      <c r="Y23" s="162"/>
-      <c r="Z23" s="162"/>
-      <c r="AA23" s="162"/>
-      <c r="AB23" s="162"/>
-      <c r="AC23" s="162"/>
-      <c r="AD23" s="162"/>
-      <c r="AE23" s="162"/>
-      <c r="AF23" s="162"/>
-      <c r="AG23" s="162"/>
-      <c r="AH23" s="162"/>
-      <c r="AI23" s="162"/>
-      <c r="AJ23" s="162"/>
-      <c r="AK23" s="162"/>
-      <c r="AL23" s="162"/>
-      <c r="AM23" s="162"/>
-      <c r="AN23" s="162"/>
-      <c r="AO23" s="162"/>
-      <c r="AP23" s="162"/>
-      <c r="AQ23" s="162"/>
-      <c r="AR23" s="162"/>
-      <c r="AS23" s="162"/>
-      <c r="AT23" s="162"/>
-      <c r="AU23" s="162"/>
-      <c r="AV23" s="162"/>
-      <c r="AW23" s="162"/>
-      <c r="AX23" s="162"/>
-      <c r="AY23" s="162"/>
-      <c r="AZ23" s="162"/>
-      <c r="BA23" s="162"/>
-      <c r="BB23" s="162"/>
-      <c r="BC23" s="162"/>
-      <c r="BD23" s="162"/>
-      <c r="BE23" s="162"/>
-      <c r="BF23" s="162"/>
-      <c r="BG23" s="162"/>
-      <c r="BH23" s="162"/>
-      <c r="BI23" s="162"/>
-      <c r="BJ23" s="162"/>
-      <c r="BK23" s="163"/>
+      <c r="C23" s="173"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="173"/>
+      <c r="G23" s="173"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="173"/>
+      <c r="J23" s="173"/>
+      <c r="K23" s="173"/>
+      <c r="L23" s="173"/>
+      <c r="M23" s="173"/>
+      <c r="N23" s="173"/>
+      <c r="O23" s="173"/>
+      <c r="P23" s="173"/>
+      <c r="Q23" s="173"/>
+      <c r="R23" s="173"/>
+      <c r="S23" s="173"/>
+      <c r="T23" s="173"/>
+      <c r="U23" s="173"/>
+      <c r="V23" s="173"/>
+      <c r="W23" s="173"/>
+      <c r="X23" s="173"/>
+      <c r="Y23" s="173"/>
+      <c r="Z23" s="173"/>
+      <c r="AA23" s="173"/>
+      <c r="AB23" s="173"/>
+      <c r="AC23" s="173"/>
+      <c r="AD23" s="173"/>
+      <c r="AE23" s="173"/>
+      <c r="AF23" s="173"/>
+      <c r="AG23" s="173"/>
+      <c r="AH23" s="173"/>
+      <c r="AI23" s="173"/>
+      <c r="AJ23" s="173"/>
+      <c r="AK23" s="173"/>
+      <c r="AL23" s="173"/>
+      <c r="AM23" s="173"/>
+      <c r="AN23" s="173"/>
+      <c r="AO23" s="173"/>
+      <c r="AP23" s="173"/>
+      <c r="AQ23" s="173"/>
+      <c r="AR23" s="173"/>
+      <c r="AS23" s="173"/>
+      <c r="AT23" s="173"/>
+      <c r="AU23" s="173"/>
+      <c r="AV23" s="173"/>
+      <c r="AW23" s="173"/>
+      <c r="AX23" s="173"/>
+      <c r="AY23" s="173"/>
+      <c r="AZ23" s="173"/>
+      <c r="BA23" s="173"/>
+      <c r="BB23" s="173"/>
+      <c r="BC23" s="173"/>
+      <c r="BD23" s="173"/>
+      <c r="BE23" s="173"/>
+      <c r="BF23" s="173"/>
+      <c r="BG23" s="173"/>
+      <c r="BH23" s="173"/>
+      <c r="BI23" s="173"/>
+      <c r="BJ23" s="173"/>
+      <c r="BK23" s="174"/>
     </row>
     <row r="24" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B24" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="109"/>
-      <c r="D24" s="109"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="16"/>
@@ -2843,8 +2840,8 @@
       <c r="B25" s="46">
         <v>1</v>
       </c>
-      <c r="C25" s="105" t="s">
-        <v>37</v>
+      <c r="C25" s="104" t="s">
+        <v>36</v>
       </c>
       <c r="D25" s="22"/>
       <c r="E25" s="48"/>
@@ -2885,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="AR25" s="52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AY25" s="37"/>
       <c r="BK25" s="8"/>
@@ -2933,8 +2930,8 @@
       <c r="B27" s="46">
         <v>3</v>
       </c>
-      <c r="C27" s="106" t="s">
-        <v>38</v>
+      <c r="C27" s="105" t="s">
+        <v>37</v>
       </c>
       <c r="D27" s="53"/>
       <c r="E27" s="48"/>
@@ -2975,7 +2972,7 @@
         <v>3</v>
       </c>
       <c r="AR27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AU27" s="22"/>
       <c r="AY27" s="22"/>
@@ -3022,7 +3019,7 @@
       <c r="AO28" s="49"/>
       <c r="AP28" s="7"/>
       <c r="AQ28" s="54"/>
-      <c r="AR28" s="101"/>
+      <c r="AR28" s="100"/>
       <c r="AS28" s="55"/>
       <c r="AU28" s="22"/>
       <c r="AY28" s="22"/>
@@ -3066,8 +3063,8 @@
       <c r="BP29" s="22"/>
     </row>
     <row r="30" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="158" t="s">
-        <v>44</v>
+      <c r="B30" s="157" t="s">
+        <v>43</v>
       </c>
       <c r="C30" s="33"/>
       <c r="D30" s="22"/>
@@ -3093,45 +3090,45 @@
       <c r="BP30" s="37"/>
     </row>
     <row r="31" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="143"/>
-      <c r="C31" s="114"/>
-      <c r="D31" s="144"/>
-      <c r="E31" s="144"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="144"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="144"/>
-      <c r="L31" s="144"/>
-      <c r="M31" s="144"/>
-      <c r="N31" s="144"/>
-      <c r="O31" s="144"/>
-      <c r="P31" s="144"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="144"/>
-      <c r="S31" s="144"/>
-      <c r="T31" s="144"/>
-      <c r="U31" s="144"/>
-      <c r="V31" s="144"/>
-      <c r="W31" s="144"/>
-      <c r="X31" s="144"/>
-      <c r="Y31" s="144"/>
-      <c r="Z31" s="144"/>
-      <c r="AA31" s="144"/>
-      <c r="AB31" s="144"/>
-      <c r="AC31" s="144"/>
-      <c r="AD31" s="144"/>
-      <c r="AE31" s="144"/>
-      <c r="AF31" s="144"/>
-      <c r="AG31" s="144"/>
-      <c r="AH31" s="144"/>
-      <c r="AI31" s="144"/>
-      <c r="AJ31" s="144"/>
-      <c r="AK31" s="144"/>
-      <c r="AL31" s="144"/>
-      <c r="AM31" s="144"/>
-      <c r="AN31" s="144"/>
+      <c r="B31" s="142"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="143"/>
+      <c r="E31" s="143"/>
+      <c r="F31" s="143"/>
+      <c r="G31" s="143"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="143"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="143"/>
+      <c r="Q31" s="143"/>
+      <c r="R31" s="143"/>
+      <c r="S31" s="143"/>
+      <c r="T31" s="143"/>
+      <c r="U31" s="143"/>
+      <c r="V31" s="143"/>
+      <c r="W31" s="143"/>
+      <c r="X31" s="143"/>
+      <c r="Y31" s="143"/>
+      <c r="Z31" s="143"/>
+      <c r="AA31" s="143"/>
+      <c r="AB31" s="143"/>
+      <c r="AC31" s="143"/>
+      <c r="AD31" s="143"/>
+      <c r="AE31" s="143"/>
+      <c r="AF31" s="143"/>
+      <c r="AG31" s="143"/>
+      <c r="AH31" s="143"/>
+      <c r="AI31" s="143"/>
+      <c r="AJ31" s="143"/>
+      <c r="AK31" s="143"/>
+      <c r="AL31" s="143"/>
+      <c r="AM31" s="143"/>
+      <c r="AN31" s="143"/>
       <c r="AO31" s="49"/>
       <c r="AP31" s="7"/>
       <c r="AQ31" s="51">
@@ -3155,45 +3152,45 @@
       <c r="BP31" s="37"/>
     </row>
     <row r="32" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="142"/>
-      <c r="C32" s="114"/>
-      <c r="D32" s="144"/>
-      <c r="E32" s="144"/>
-      <c r="F32" s="144"/>
-      <c r="G32" s="144"/>
-      <c r="H32" s="144"/>
-      <c r="I32" s="144"/>
-      <c r="J32" s="144"/>
-      <c r="K32" s="144"/>
-      <c r="L32" s="144"/>
-      <c r="M32" s="144"/>
-      <c r="N32" s="144"/>
-      <c r="O32" s="144"/>
-      <c r="P32" s="144"/>
-      <c r="Q32" s="144"/>
-      <c r="R32" s="144"/>
-      <c r="S32" s="144"/>
-      <c r="T32" s="144"/>
-      <c r="U32" s="144"/>
-      <c r="V32" s="144"/>
-      <c r="W32" s="144"/>
-      <c r="X32" s="144"/>
-      <c r="Y32" s="144"/>
-      <c r="Z32" s="144"/>
-      <c r="AA32" s="144"/>
-      <c r="AB32" s="144"/>
-      <c r="AC32" s="144"/>
-      <c r="AD32" s="144"/>
-      <c r="AE32" s="144"/>
-      <c r="AF32" s="144"/>
-      <c r="AG32" s="144"/>
-      <c r="AH32" s="144"/>
-      <c r="AI32" s="144"/>
-      <c r="AJ32" s="144"/>
-      <c r="AK32" s="144"/>
-      <c r="AL32" s="144"/>
-      <c r="AM32" s="144"/>
-      <c r="AN32" s="144"/>
+      <c r="B32" s="141"/>
+      <c r="C32" s="113"/>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="143"/>
+      <c r="G32" s="143"/>
+      <c r="H32" s="143"/>
+      <c r="I32" s="143"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="143"/>
+      <c r="L32" s="143"/>
+      <c r="M32" s="143"/>
+      <c r="N32" s="143"/>
+      <c r="O32" s="143"/>
+      <c r="P32" s="143"/>
+      <c r="Q32" s="143"/>
+      <c r="R32" s="143"/>
+      <c r="S32" s="143"/>
+      <c r="T32" s="143"/>
+      <c r="U32" s="143"/>
+      <c r="V32" s="143"/>
+      <c r="W32" s="143"/>
+      <c r="X32" s="143"/>
+      <c r="Y32" s="143"/>
+      <c r="Z32" s="143"/>
+      <c r="AA32" s="143"/>
+      <c r="AB32" s="143"/>
+      <c r="AC32" s="143"/>
+      <c r="AD32" s="143"/>
+      <c r="AE32" s="143"/>
+      <c r="AF32" s="143"/>
+      <c r="AG32" s="143"/>
+      <c r="AH32" s="143"/>
+      <c r="AI32" s="143"/>
+      <c r="AJ32" s="143"/>
+      <c r="AK32" s="143"/>
+      <c r="AL32" s="143"/>
+      <c r="AM32" s="143"/>
+      <c r="AN32" s="143"/>
       <c r="AO32" s="49"/>
       <c r="AP32" s="7"/>
       <c r="AQ32" s="46">
@@ -3217,45 +3214,45 @@
       <c r="BP32" s="37"/>
     </row>
     <row r="33" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="143"/>
-      <c r="C33" s="114"/>
-      <c r="D33" s="144"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="145"/>
-      <c r="H33" s="145"/>
-      <c r="I33" s="145"/>
-      <c r="J33" s="145"/>
-      <c r="K33" s="145"/>
-      <c r="L33" s="145"/>
-      <c r="M33" s="145"/>
-      <c r="N33" s="145"/>
-      <c r="O33" s="144"/>
-      <c r="P33" s="145"/>
-      <c r="Q33" s="145"/>
-      <c r="R33" s="145"/>
-      <c r="S33" s="145"/>
-      <c r="T33" s="145"/>
-      <c r="U33" s="144"/>
-      <c r="V33" s="144"/>
-      <c r="W33" s="144"/>
-      <c r="X33" s="144"/>
-      <c r="Y33" s="144"/>
-      <c r="Z33" s="144"/>
-      <c r="AA33" s="144"/>
-      <c r="AB33" s="144"/>
-      <c r="AC33" s="144"/>
-      <c r="AD33" s="144"/>
-      <c r="AE33" s="144"/>
-      <c r="AF33" s="144"/>
-      <c r="AG33" s="144"/>
-      <c r="AH33" s="144"/>
-      <c r="AI33" s="144"/>
-      <c r="AJ33" s="144"/>
-      <c r="AK33" s="144"/>
-      <c r="AL33" s="144"/>
-      <c r="AM33" s="144"/>
-      <c r="AN33" s="144"/>
+      <c r="B33" s="142"/>
+      <c r="C33" s="113"/>
+      <c r="D33" s="143"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="144"/>
+      <c r="G33" s="144"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="144"/>
+      <c r="J33" s="144"/>
+      <c r="K33" s="144"/>
+      <c r="L33" s="144"/>
+      <c r="M33" s="144"/>
+      <c r="N33" s="144"/>
+      <c r="O33" s="143"/>
+      <c r="P33" s="144"/>
+      <c r="Q33" s="144"/>
+      <c r="R33" s="144"/>
+      <c r="S33" s="144"/>
+      <c r="T33" s="144"/>
+      <c r="U33" s="143"/>
+      <c r="V33" s="143"/>
+      <c r="W33" s="143"/>
+      <c r="X33" s="143"/>
+      <c r="Y33" s="143"/>
+      <c r="Z33" s="143"/>
+      <c r="AA33" s="143"/>
+      <c r="AB33" s="143"/>
+      <c r="AC33" s="143"/>
+      <c r="AD33" s="143"/>
+      <c r="AE33" s="143"/>
+      <c r="AF33" s="143"/>
+      <c r="AG33" s="143"/>
+      <c r="AH33" s="143"/>
+      <c r="AI33" s="143"/>
+      <c r="AJ33" s="143"/>
+      <c r="AK33" s="143"/>
+      <c r="AL33" s="143"/>
+      <c r="AM33" s="143"/>
+      <c r="AN33" s="143"/>
       <c r="AO33" s="8"/>
       <c r="AP33" s="7"/>
       <c r="AQ33" s="51">
@@ -3267,45 +3264,45 @@
       <c r="BN33" s="57"/>
     </row>
     <row r="34" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="142"/>
-      <c r="C34" s="114"/>
-      <c r="D34" s="146"/>
-      <c r="E34" s="146"/>
-      <c r="F34" s="147"/>
-      <c r="G34" s="147"/>
-      <c r="H34" s="147"/>
-      <c r="I34" s="147"/>
-      <c r="J34" s="147"/>
-      <c r="K34" s="147"/>
-      <c r="L34" s="147"/>
-      <c r="M34" s="147"/>
-      <c r="N34" s="147"/>
-      <c r="O34" s="144"/>
-      <c r="P34" s="147"/>
-      <c r="Q34" s="147"/>
-      <c r="R34" s="147"/>
-      <c r="S34" s="147"/>
-      <c r="T34" s="147"/>
-      <c r="U34" s="146"/>
-      <c r="V34" s="146"/>
-      <c r="W34" s="146"/>
-      <c r="X34" s="146"/>
-      <c r="Y34" s="146"/>
-      <c r="Z34" s="146"/>
-      <c r="AA34" s="146"/>
-      <c r="AB34" s="146"/>
-      <c r="AC34" s="146"/>
-      <c r="AD34" s="146"/>
-      <c r="AE34" s="144"/>
-      <c r="AF34" s="144"/>
-      <c r="AG34" s="144"/>
-      <c r="AH34" s="144"/>
-      <c r="AI34" s="144"/>
-      <c r="AJ34" s="144"/>
-      <c r="AK34" s="144"/>
-      <c r="AL34" s="144"/>
-      <c r="AM34" s="144"/>
-      <c r="AN34" s="144"/>
+      <c r="B34" s="141"/>
+      <c r="C34" s="113"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="145"/>
+      <c r="F34" s="146"/>
+      <c r="G34" s="146"/>
+      <c r="H34" s="146"/>
+      <c r="I34" s="146"/>
+      <c r="J34" s="146"/>
+      <c r="K34" s="146"/>
+      <c r="L34" s="146"/>
+      <c r="M34" s="146"/>
+      <c r="N34" s="146"/>
+      <c r="O34" s="143"/>
+      <c r="P34" s="146"/>
+      <c r="Q34" s="146"/>
+      <c r="R34" s="146"/>
+      <c r="S34" s="146"/>
+      <c r="T34" s="146"/>
+      <c r="U34" s="145"/>
+      <c r="V34" s="145"/>
+      <c r="W34" s="145"/>
+      <c r="X34" s="145"/>
+      <c r="Y34" s="145"/>
+      <c r="Z34" s="145"/>
+      <c r="AA34" s="145"/>
+      <c r="AB34" s="145"/>
+      <c r="AC34" s="145"/>
+      <c r="AD34" s="145"/>
+      <c r="AE34" s="143"/>
+      <c r="AF34" s="143"/>
+      <c r="AG34" s="143"/>
+      <c r="AH34" s="143"/>
+      <c r="AI34" s="143"/>
+      <c r="AJ34" s="143"/>
+      <c r="AK34" s="143"/>
+      <c r="AL34" s="143"/>
+      <c r="AM34" s="143"/>
+      <c r="AN34" s="143"/>
       <c r="AO34" s="8"/>
       <c r="AP34" s="7"/>
       <c r="AQ34" s="46">
@@ -3318,45 +3315,45 @@
       <c r="BO34" s="22"/>
     </row>
     <row r="35" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="143"/>
-      <c r="C35" s="148"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="145"/>
-      <c r="G35" s="145"/>
-      <c r="H35" s="145"/>
-      <c r="I35" s="145"/>
-      <c r="J35" s="145"/>
-      <c r="K35" s="145"/>
-      <c r="L35" s="145"/>
-      <c r="M35" s="145"/>
-      <c r="N35" s="145"/>
-      <c r="O35" s="144"/>
-      <c r="P35" s="145"/>
-      <c r="Q35" s="145"/>
-      <c r="R35" s="145"/>
-      <c r="S35" s="145"/>
-      <c r="T35" s="145"/>
-      <c r="U35" s="144"/>
-      <c r="V35" s="144"/>
-      <c r="W35" s="144"/>
-      <c r="X35" s="144"/>
-      <c r="Y35" s="144"/>
-      <c r="Z35" s="144"/>
-      <c r="AA35" s="144"/>
-      <c r="AB35" s="144"/>
-      <c r="AC35" s="144"/>
-      <c r="AD35" s="144"/>
-      <c r="AE35" s="144"/>
-      <c r="AF35" s="144"/>
-      <c r="AG35" s="144"/>
-      <c r="AH35" s="144"/>
-      <c r="AI35" s="144"/>
-      <c r="AJ35" s="144"/>
-      <c r="AK35" s="144"/>
-      <c r="AL35" s="144"/>
-      <c r="AM35" s="144"/>
-      <c r="AN35" s="144"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="147"/>
+      <c r="D35" s="143"/>
+      <c r="E35" s="143"/>
+      <c r="F35" s="144"/>
+      <c r="G35" s="144"/>
+      <c r="H35" s="144"/>
+      <c r="I35" s="144"/>
+      <c r="J35" s="144"/>
+      <c r="K35" s="144"/>
+      <c r="L35" s="144"/>
+      <c r="M35" s="144"/>
+      <c r="N35" s="144"/>
+      <c r="O35" s="143"/>
+      <c r="P35" s="144"/>
+      <c r="Q35" s="144"/>
+      <c r="R35" s="144"/>
+      <c r="S35" s="144"/>
+      <c r="T35" s="144"/>
+      <c r="U35" s="143"/>
+      <c r="V35" s="143"/>
+      <c r="W35" s="143"/>
+      <c r="X35" s="143"/>
+      <c r="Y35" s="143"/>
+      <c r="Z35" s="143"/>
+      <c r="AA35" s="143"/>
+      <c r="AB35" s="143"/>
+      <c r="AC35" s="143"/>
+      <c r="AD35" s="143"/>
+      <c r="AE35" s="143"/>
+      <c r="AF35" s="143"/>
+      <c r="AG35" s="143"/>
+      <c r="AH35" s="143"/>
+      <c r="AI35" s="143"/>
+      <c r="AJ35" s="143"/>
+      <c r="AK35" s="143"/>
+      <c r="AL35" s="143"/>
+      <c r="AM35" s="143"/>
+      <c r="AN35" s="143"/>
       <c r="AO35" s="8"/>
       <c r="AP35" s="7"/>
       <c r="AQ35" s="51">
@@ -3369,45 +3366,45 @@
       <c r="BN35" s="57"/>
     </row>
     <row r="36" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="142"/>
-      <c r="C36" s="149"/>
-      <c r="D36" s="144"/>
-      <c r="E36" s="144"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="145"/>
-      <c r="H36" s="145"/>
-      <c r="I36" s="145"/>
-      <c r="J36" s="145"/>
-      <c r="K36" s="145"/>
-      <c r="L36" s="145"/>
-      <c r="M36" s="145"/>
-      <c r="N36" s="145"/>
-      <c r="O36" s="144"/>
-      <c r="P36" s="145"/>
-      <c r="Q36" s="145"/>
-      <c r="R36" s="145"/>
-      <c r="S36" s="145"/>
-      <c r="T36" s="145"/>
-      <c r="U36" s="144"/>
-      <c r="V36" s="144"/>
-      <c r="W36" s="144"/>
-      <c r="X36" s="144"/>
-      <c r="Y36" s="144"/>
-      <c r="Z36" s="144"/>
-      <c r="AA36" s="144"/>
-      <c r="AB36" s="144"/>
-      <c r="AC36" s="144"/>
-      <c r="AD36" s="144"/>
-      <c r="AE36" s="144"/>
+      <c r="B36" s="141"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="143"/>
+      <c r="E36" s="143"/>
+      <c r="F36" s="144"/>
+      <c r="G36" s="144"/>
+      <c r="H36" s="144"/>
+      <c r="I36" s="144"/>
+      <c r="J36" s="144"/>
+      <c r="K36" s="144"/>
+      <c r="L36" s="144"/>
+      <c r="M36" s="144"/>
+      <c r="N36" s="144"/>
+      <c r="O36" s="143"/>
+      <c r="P36" s="144"/>
+      <c r="Q36" s="144"/>
+      <c r="R36" s="144"/>
+      <c r="S36" s="144"/>
+      <c r="T36" s="144"/>
+      <c r="U36" s="143"/>
+      <c r="V36" s="143"/>
+      <c r="W36" s="143"/>
+      <c r="X36" s="143"/>
+      <c r="Y36" s="143"/>
+      <c r="Z36" s="143"/>
+      <c r="AA36" s="143"/>
+      <c r="AB36" s="143"/>
+      <c r="AC36" s="143"/>
+      <c r="AD36" s="143"/>
+      <c r="AE36" s="143"/>
       <c r="AF36" s="37"/>
       <c r="AG36" s="37"/>
       <c r="AH36" s="37"/>
       <c r="AI36" s="37"/>
       <c r="AJ36" s="37"/>
       <c r="AK36" s="37"/>
-      <c r="AL36" s="144"/>
-      <c r="AM36" s="144"/>
-      <c r="AN36" s="144"/>
+      <c r="AL36" s="143"/>
+      <c r="AM36" s="143"/>
+      <c r="AN36" s="143"/>
       <c r="AO36" s="8"/>
       <c r="AP36" s="7"/>
       <c r="AQ36" s="46">
@@ -3420,45 +3417,45 @@
       <c r="BP36" s="22"/>
     </row>
     <row r="37" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="143"/>
-      <c r="C37" s="148"/>
-      <c r="D37" s="144"/>
-      <c r="E37" s="144"/>
-      <c r="F37" s="145"/>
-      <c r="G37" s="145"/>
-      <c r="H37" s="145"/>
-      <c r="I37" s="145"/>
-      <c r="J37" s="145"/>
-      <c r="K37" s="145"/>
-      <c r="L37" s="145"/>
-      <c r="M37" s="145"/>
-      <c r="N37" s="145"/>
-      <c r="O37" s="144"/>
-      <c r="P37" s="145"/>
-      <c r="Q37" s="145"/>
-      <c r="R37" s="145"/>
-      <c r="S37" s="145"/>
-      <c r="T37" s="145"/>
-      <c r="U37" s="144"/>
-      <c r="V37" s="144"/>
-      <c r="W37" s="144"/>
-      <c r="X37" s="144"/>
-      <c r="Y37" s="144"/>
-      <c r="Z37" s="144"/>
-      <c r="AA37" s="144"/>
-      <c r="AB37" s="144"/>
-      <c r="AC37" s="144"/>
-      <c r="AD37" s="144"/>
-      <c r="AE37" s="144"/>
+      <c r="B37" s="142"/>
+      <c r="C37" s="147"/>
+      <c r="D37" s="143"/>
+      <c r="E37" s="143"/>
+      <c r="F37" s="144"/>
+      <c r="G37" s="144"/>
+      <c r="H37" s="144"/>
+      <c r="I37" s="144"/>
+      <c r="J37" s="144"/>
+      <c r="K37" s="144"/>
+      <c r="L37" s="144"/>
+      <c r="M37" s="144"/>
+      <c r="N37" s="144"/>
+      <c r="O37" s="143"/>
+      <c r="P37" s="144"/>
+      <c r="Q37" s="144"/>
+      <c r="R37" s="144"/>
+      <c r="S37" s="144"/>
+      <c r="T37" s="144"/>
+      <c r="U37" s="143"/>
+      <c r="V37" s="143"/>
+      <c r="W37" s="143"/>
+      <c r="X37" s="143"/>
+      <c r="Y37" s="143"/>
+      <c r="Z37" s="143"/>
+      <c r="AA37" s="143"/>
+      <c r="AB37" s="143"/>
+      <c r="AC37" s="143"/>
+      <c r="AD37" s="143"/>
+      <c r="AE37" s="143"/>
       <c r="AF37" s="37"/>
       <c r="AG37" s="37"/>
       <c r="AH37" s="37"/>
       <c r="AI37" s="37"/>
       <c r="AJ37" s="37"/>
       <c r="AK37" s="37"/>
-      <c r="AL37" s="144"/>
-      <c r="AM37" s="144"/>
-      <c r="AN37" s="144"/>
+      <c r="AL37" s="143"/>
+      <c r="AM37" s="143"/>
+      <c r="AN37" s="143"/>
       <c r="AO37" s="8"/>
       <c r="AP37" s="7"/>
       <c r="AQ37" s="51">
@@ -3470,121 +3467,121 @@
       <c r="BK37" s="8"/>
     </row>
     <row r="38" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="190"/>
-      <c r="C38" s="188"/>
-      <c r="D38" s="189"/>
-      <c r="E38" s="144"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="145"/>
-      <c r="H38" s="145"/>
-      <c r="I38" s="145"/>
-      <c r="J38" s="145"/>
-      <c r="K38" s="145"/>
-      <c r="L38" s="145"/>
-      <c r="M38" s="145"/>
-      <c r="N38" s="145"/>
-      <c r="O38" s="145"/>
-      <c r="P38" s="145"/>
-      <c r="Q38" s="145"/>
-      <c r="R38" s="145"/>
-      <c r="S38" s="145"/>
-      <c r="T38" s="145"/>
-      <c r="U38" s="144"/>
-      <c r="V38" s="144"/>
-      <c r="W38" s="144"/>
-      <c r="X38" s="144"/>
-      <c r="Y38" s="144"/>
-      <c r="Z38" s="144"/>
-      <c r="AA38" s="144"/>
-      <c r="AB38" s="144"/>
-      <c r="AC38" s="144"/>
-      <c r="AD38" s="144"/>
-      <c r="AE38" s="144"/>
-      <c r="AF38" s="144"/>
-      <c r="AG38" s="144"/>
-      <c r="AH38" s="144"/>
-      <c r="AI38" s="144"/>
-      <c r="AJ38" s="144"/>
-      <c r="AK38" s="144"/>
-      <c r="AL38" s="144"/>
-      <c r="AM38" s="144"/>
-      <c r="AN38" s="144"/>
+      <c r="B38" s="161"/>
+      <c r="C38" s="159"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="143"/>
+      <c r="F38" s="144"/>
+      <c r="G38" s="144"/>
+      <c r="H38" s="144"/>
+      <c r="I38" s="144"/>
+      <c r="J38" s="144"/>
+      <c r="K38" s="144"/>
+      <c r="L38" s="144"/>
+      <c r="M38" s="144"/>
+      <c r="N38" s="144"/>
+      <c r="O38" s="144"/>
+      <c r="P38" s="144"/>
+      <c r="Q38" s="144"/>
+      <c r="R38" s="144"/>
+      <c r="S38" s="144"/>
+      <c r="T38" s="144"/>
+      <c r="U38" s="143"/>
+      <c r="V38" s="143"/>
+      <c r="W38" s="143"/>
+      <c r="X38" s="143"/>
+      <c r="Y38" s="143"/>
+      <c r="Z38" s="143"/>
+      <c r="AA38" s="143"/>
+      <c r="AB38" s="143"/>
+      <c r="AC38" s="143"/>
+      <c r="AD38" s="143"/>
+      <c r="AE38" s="143"/>
+      <c r="AF38" s="143"/>
+      <c r="AG38" s="143"/>
+      <c r="AH38" s="143"/>
+      <c r="AI38" s="143"/>
+      <c r="AJ38" s="143"/>
+      <c r="AK38" s="143"/>
+      <c r="AL38" s="143"/>
+      <c r="AM38" s="143"/>
+      <c r="AN38" s="143"/>
       <c r="AO38" s="8"/>
       <c r="AP38" s="38"/>
-      <c r="AQ38" s="190"/>
+      <c r="AQ38" s="161"/>
       <c r="AR38" s="33"/>
       <c r="BK38" s="8"/>
     </row>
     <row r="39" spans="1:87" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="191"/>
+      <c r="B39" s="162"/>
       <c r="C39" s="62"/>
       <c r="D39" s="31"/>
       <c r="E39" s="58"/>
     </row>
     <row r="40" spans="1:87" s="1" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="166"/>
-      <c r="C40" s="166"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="166"/>
-      <c r="F40" s="166"/>
-      <c r="G40" s="166"/>
-      <c r="H40" s="166"/>
-      <c r="I40" s="166"/>
-      <c r="J40" s="166"/>
-      <c r="K40" s="166"/>
-      <c r="L40" s="166"/>
-      <c r="M40" s="166"/>
-      <c r="N40" s="166"/>
-      <c r="O40" s="166"/>
-      <c r="P40" s="166"/>
-      <c r="Q40" s="166"/>
-      <c r="R40" s="166"/>
-      <c r="S40" s="166"/>
-      <c r="T40" s="166"/>
-      <c r="U40" s="166"/>
-      <c r="V40" s="166"/>
-      <c r="W40" s="166"/>
-      <c r="X40" s="166"/>
-      <c r="Y40" s="166"/>
-      <c r="Z40" s="166"/>
-      <c r="AA40" s="166"/>
-      <c r="AB40" s="166"/>
-      <c r="AC40" s="166"/>
-      <c r="AD40" s="166"/>
-      <c r="AE40" s="166"/>
-      <c r="AF40" s="166"/>
-      <c r="AG40" s="166"/>
-      <c r="AH40" s="166"/>
-      <c r="AI40" s="166"/>
-      <c r="AJ40" s="166"/>
-      <c r="AK40" s="166"/>
-      <c r="AL40" s="166"/>
-      <c r="AM40" s="166"/>
-      <c r="AN40" s="166"/>
-      <c r="AO40" s="166"/>
-      <c r="AP40" s="166"/>
-      <c r="AQ40" s="166"/>
-      <c r="AR40" s="166"/>
-      <c r="AS40" s="166"/>
-      <c r="AT40" s="166"/>
-      <c r="AU40" s="166"/>
-      <c r="AV40" s="166"/>
-      <c r="AW40" s="166"/>
-      <c r="AX40" s="166"/>
-      <c r="AY40" s="166"/>
-      <c r="AZ40" s="166"/>
-      <c r="BA40" s="166"/>
-      <c r="BB40" s="166"/>
-      <c r="BC40" s="166"/>
-      <c r="BD40" s="166"/>
-      <c r="BE40" s="166"/>
-      <c r="BF40" s="166"/>
-      <c r="BG40" s="166"/>
-      <c r="BH40" s="166"/>
-      <c r="BI40" s="166"/>
-      <c r="BJ40" s="166"/>
-      <c r="BK40" s="166"/>
+      <c r="B40" s="186"/>
+      <c r="C40" s="186"/>
+      <c r="D40" s="186"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
+      <c r="G40" s="186"/>
+      <c r="H40" s="186"/>
+      <c r="I40" s="186"/>
+      <c r="J40" s="186"/>
+      <c r="K40" s="186"/>
+      <c r="L40" s="186"/>
+      <c r="M40" s="186"/>
+      <c r="N40" s="186"/>
+      <c r="O40" s="186"/>
+      <c r="P40" s="186"/>
+      <c r="Q40" s="186"/>
+      <c r="R40" s="186"/>
+      <c r="S40" s="186"/>
+      <c r="T40" s="186"/>
+      <c r="U40" s="186"/>
+      <c r="V40" s="186"/>
+      <c r="W40" s="186"/>
+      <c r="X40" s="186"/>
+      <c r="Y40" s="186"/>
+      <c r="Z40" s="186"/>
+      <c r="AA40" s="186"/>
+      <c r="AB40" s="186"/>
+      <c r="AC40" s="186"/>
+      <c r="AD40" s="186"/>
+      <c r="AE40" s="186"/>
+      <c r="AF40" s="186"/>
+      <c r="AG40" s="186"/>
+      <c r="AH40" s="186"/>
+      <c r="AI40" s="186"/>
+      <c r="AJ40" s="186"/>
+      <c r="AK40" s="186"/>
+      <c r="AL40" s="186"/>
+      <c r="AM40" s="186"/>
+      <c r="AN40" s="186"/>
+      <c r="AO40" s="186"/>
+      <c r="AP40" s="186"/>
+      <c r="AQ40" s="186"/>
+      <c r="AR40" s="186"/>
+      <c r="AS40" s="186"/>
+      <c r="AT40" s="186"/>
+      <c r="AU40" s="186"/>
+      <c r="AV40" s="186"/>
+      <c r="AW40" s="186"/>
+      <c r="AX40" s="186"/>
+      <c r="AY40" s="186"/>
+      <c r="AZ40" s="186"/>
+      <c r="BA40" s="186"/>
+      <c r="BB40" s="186"/>
+      <c r="BC40" s="186"/>
+      <c r="BD40" s="186"/>
+      <c r="BE40" s="186"/>
+      <c r="BF40" s="186"/>
+      <c r="BG40" s="186"/>
+      <c r="BH40" s="186"/>
+      <c r="BI40" s="186"/>
+      <c r="BJ40" s="186"/>
+      <c r="BK40" s="186"/>
       <c r="BL40" s="2"/>
     </row>
     <row r="41" spans="1:87" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -3599,188 +3596,188 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="170" t="s">
+      <c r="M41" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="N41" s="171"/>
-      <c r="O41" s="171"/>
-      <c r="P41" s="171"/>
-      <c r="Q41" s="171"/>
-      <c r="R41" s="171"/>
-      <c r="S41" s="171"/>
-      <c r="T41" s="171"/>
-      <c r="U41" s="171"/>
-      <c r="V41" s="171"/>
-      <c r="W41" s="171"/>
-      <c r="X41" s="171"/>
-      <c r="Y41" s="171"/>
-      <c r="Z41" s="171"/>
-      <c r="AA41" s="171"/>
-      <c r="AB41" s="171"/>
-      <c r="AC41" s="171"/>
-      <c r="AD41" s="171"/>
-      <c r="AE41" s="171"/>
-      <c r="AF41" s="171"/>
-      <c r="AG41" s="171"/>
-      <c r="AH41" s="171"/>
-      <c r="AI41" s="171"/>
-      <c r="AJ41" s="171"/>
-      <c r="AK41" s="171"/>
-      <c r="AL41" s="171"/>
-      <c r="AM41" s="171"/>
-      <c r="AN41" s="171"/>
-      <c r="AO41" s="172"/>
-      <c r="AP41" s="154"/>
-      <c r="AQ41" s="132" t="str">
+      <c r="N41" s="164"/>
+      <c r="O41" s="164"/>
+      <c r="P41" s="164"/>
+      <c r="Q41" s="164"/>
+      <c r="R41" s="164"/>
+      <c r="S41" s="164"/>
+      <c r="T41" s="164"/>
+      <c r="U41" s="164"/>
+      <c r="V41" s="164"/>
+      <c r="W41" s="164"/>
+      <c r="X41" s="164"/>
+      <c r="Y41" s="164"/>
+      <c r="Z41" s="164"/>
+      <c r="AA41" s="164"/>
+      <c r="AB41" s="164"/>
+      <c r="AC41" s="164"/>
+      <c r="AD41" s="164"/>
+      <c r="AE41" s="164"/>
+      <c r="AF41" s="164"/>
+      <c r="AG41" s="164"/>
+      <c r="AH41" s="164"/>
+      <c r="AI41" s="164"/>
+      <c r="AJ41" s="164"/>
+      <c r="AK41" s="164"/>
+      <c r="AL41" s="164"/>
+      <c r="AM41" s="164"/>
+      <c r="AN41" s="164"/>
+      <c r="AO41" s="165"/>
+      <c r="AP41" s="153"/>
+      <c r="AQ41" s="131" t="str">
         <f>$AQ$2</f>
         <v>Divisi</v>
       </c>
-      <c r="AR41" s="132"/>
-      <c r="AS41" s="132"/>
-      <c r="AT41" s="132"/>
-      <c r="AU41" s="132"/>
-      <c r="AV41" s="133" t="str">
+      <c r="AR41" s="131"/>
+      <c r="AS41" s="131"/>
+      <c r="AT41" s="131"/>
+      <c r="AU41" s="131"/>
+      <c r="AV41" s="132" t="str">
         <f>$AV$2</f>
         <v xml:space="preserve">:  </v>
       </c>
-      <c r="AW41" s="133" t="str">
+      <c r="AW41" s="132" t="str">
         <f>$AW$2</f>
         <v>DivisionName</v>
       </c>
-      <c r="AX41" s="132"/>
-      <c r="AY41" s="132"/>
-      <c r="AZ41" s="132"/>
-      <c r="BA41" s="132"/>
-      <c r="BB41" s="132"/>
-      <c r="BC41" s="132"/>
-      <c r="BD41" s="132"/>
-      <c r="BE41" s="132"/>
-      <c r="BF41" s="132"/>
-      <c r="BG41" s="132"/>
-      <c r="BH41" s="132"/>
-      <c r="BI41" s="132"/>
-      <c r="BJ41" s="132"/>
-      <c r="BK41" s="134"/>
+      <c r="AX41" s="131"/>
+      <c r="AY41" s="131"/>
+      <c r="AZ41" s="131"/>
+      <c r="BA41" s="131"/>
+      <c r="BB41" s="131"/>
+      <c r="BC41" s="131"/>
+      <c r="BD41" s="131"/>
+      <c r="BE41" s="131"/>
+      <c r="BF41" s="131"/>
+      <c r="BG41" s="131"/>
+      <c r="BH41" s="131"/>
+      <c r="BI41" s="131"/>
+      <c r="BJ41" s="131"/>
+      <c r="BK41" s="133"/>
       <c r="BL41" s="6"/>
     </row>
     <row r="42" spans="1:87" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="L42" s="8"/>
-      <c r="M42" s="173"/>
-      <c r="N42" s="174"/>
-      <c r="O42" s="174"/>
-      <c r="P42" s="174"/>
-      <c r="Q42" s="174"/>
-      <c r="R42" s="174"/>
-      <c r="S42" s="174"/>
-      <c r="T42" s="174"/>
-      <c r="U42" s="174"/>
-      <c r="V42" s="174"/>
-      <c r="W42" s="174"/>
-      <c r="X42" s="174"/>
-      <c r="Y42" s="174"/>
-      <c r="Z42" s="174"/>
-      <c r="AA42" s="174"/>
-      <c r="AB42" s="174"/>
-      <c r="AC42" s="174"/>
-      <c r="AD42" s="174"/>
-      <c r="AE42" s="174"/>
-      <c r="AF42" s="174"/>
-      <c r="AG42" s="174"/>
-      <c r="AH42" s="174"/>
-      <c r="AI42" s="174"/>
-      <c r="AJ42" s="174"/>
-      <c r="AK42" s="174"/>
-      <c r="AL42" s="174"/>
-      <c r="AM42" s="174"/>
-      <c r="AN42" s="174"/>
-      <c r="AO42" s="175"/>
-      <c r="AP42" s="155"/>
-      <c r="AQ42" s="113" t="str">
+      <c r="M42" s="166"/>
+      <c r="N42" s="167"/>
+      <c r="O42" s="167"/>
+      <c r="P42" s="167"/>
+      <c r="Q42" s="167"/>
+      <c r="R42" s="167"/>
+      <c r="S42" s="167"/>
+      <c r="T42" s="167"/>
+      <c r="U42" s="167"/>
+      <c r="V42" s="167"/>
+      <c r="W42" s="167"/>
+      <c r="X42" s="167"/>
+      <c r="Y42" s="167"/>
+      <c r="Z42" s="167"/>
+      <c r="AA42" s="167"/>
+      <c r="AB42" s="167"/>
+      <c r="AC42" s="167"/>
+      <c r="AD42" s="167"/>
+      <c r="AE42" s="167"/>
+      <c r="AF42" s="167"/>
+      <c r="AG42" s="167"/>
+      <c r="AH42" s="167"/>
+      <c r="AI42" s="167"/>
+      <c r="AJ42" s="167"/>
+      <c r="AK42" s="167"/>
+      <c r="AL42" s="167"/>
+      <c r="AM42" s="167"/>
+      <c r="AN42" s="167"/>
+      <c r="AO42" s="168"/>
+      <c r="AP42" s="154"/>
+      <c r="AQ42" s="112" t="str">
         <f>$AQ$4</f>
         <v>Departemen</v>
       </c>
-      <c r="AR42" s="136"/>
-      <c r="AS42" s="136"/>
-      <c r="AT42" s="136"/>
-      <c r="AU42" s="136"/>
-      <c r="AV42" s="137" t="str">
+      <c r="AR42" s="135"/>
+      <c r="AS42" s="135"/>
+      <c r="AT42" s="135"/>
+      <c r="AU42" s="135"/>
+      <c r="AV42" s="136" t="str">
         <f>$AV$4</f>
         <v xml:space="preserve">:  </v>
       </c>
-      <c r="AW42" s="137" t="str">
+      <c r="AW42" s="136" t="str">
         <f>$AW$4</f>
         <v>DepartmentName</v>
       </c>
-      <c r="AX42" s="136"/>
-      <c r="AY42" s="136"/>
-      <c r="AZ42" s="136"/>
-      <c r="BA42" s="136"/>
-      <c r="BB42" s="136"/>
-      <c r="BC42" s="136"/>
-      <c r="BD42" s="136"/>
-      <c r="BE42" s="136"/>
-      <c r="BF42" s="136"/>
-      <c r="BG42" s="136"/>
-      <c r="BH42" s="136"/>
-      <c r="BI42" s="136"/>
-      <c r="BJ42" s="136"/>
-      <c r="BK42" s="138"/>
+      <c r="AX42" s="135"/>
+      <c r="AY42" s="135"/>
+      <c r="AZ42" s="135"/>
+      <c r="BA42" s="135"/>
+      <c r="BB42" s="135"/>
+      <c r="BC42" s="135"/>
+      <c r="BD42" s="135"/>
+      <c r="BE42" s="135"/>
+      <c r="BF42" s="135"/>
+      <c r="BG42" s="135"/>
+      <c r="BH42" s="135"/>
+      <c r="BI42" s="135"/>
+      <c r="BJ42" s="135"/>
+      <c r="BK42" s="137"/>
     </row>
     <row r="43" spans="1:87" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="L43" s="8"/>
-      <c r="M43" s="173"/>
-      <c r="N43" s="174"/>
-      <c r="O43" s="174"/>
-      <c r="P43" s="174"/>
-      <c r="Q43" s="174"/>
-      <c r="R43" s="174"/>
-      <c r="S43" s="174"/>
-      <c r="T43" s="174"/>
-      <c r="U43" s="174"/>
-      <c r="V43" s="174"/>
-      <c r="W43" s="174"/>
-      <c r="X43" s="174"/>
-      <c r="Y43" s="174"/>
-      <c r="Z43" s="174"/>
-      <c r="AA43" s="174"/>
-      <c r="AB43" s="174"/>
-      <c r="AC43" s="174"/>
-      <c r="AD43" s="174"/>
-      <c r="AE43" s="174"/>
-      <c r="AF43" s="174"/>
-      <c r="AG43" s="174"/>
-      <c r="AH43" s="174"/>
-      <c r="AI43" s="174"/>
-      <c r="AJ43" s="174"/>
-      <c r="AK43" s="174"/>
-      <c r="AL43" s="174"/>
-      <c r="AM43" s="174"/>
-      <c r="AN43" s="174"/>
-      <c r="AO43" s="175"/>
-      <c r="AP43" s="156"/>
-      <c r="AQ43" s="136"/>
-      <c r="AR43" s="136"/>
-      <c r="AS43" s="136"/>
-      <c r="AT43" s="136"/>
-      <c r="AU43" s="136"/>
-      <c r="AV43" s="137"/>
-      <c r="AW43" s="137"/>
-      <c r="AX43" s="136"/>
-      <c r="AY43" s="136"/>
-      <c r="AZ43" s="136"/>
-      <c r="BA43" s="136"/>
-      <c r="BB43" s="136"/>
-      <c r="BC43" s="136"/>
-      <c r="BD43" s="136"/>
-      <c r="BE43" s="136"/>
-      <c r="BF43" s="136"/>
-      <c r="BG43" s="136"/>
-      <c r="BH43" s="136"/>
-      <c r="BI43" s="136"/>
-      <c r="BJ43" s="136"/>
-      <c r="BK43" s="138"/>
+      <c r="M43" s="166"/>
+      <c r="N43" s="167"/>
+      <c r="O43" s="167"/>
+      <c r="P43" s="167"/>
+      <c r="Q43" s="167"/>
+      <c r="R43" s="167"/>
+      <c r="S43" s="167"/>
+      <c r="T43" s="167"/>
+      <c r="U43" s="167"/>
+      <c r="V43" s="167"/>
+      <c r="W43" s="167"/>
+      <c r="X43" s="167"/>
+      <c r="Y43" s="167"/>
+      <c r="Z43" s="167"/>
+      <c r="AA43" s="167"/>
+      <c r="AB43" s="167"/>
+      <c r="AC43" s="167"/>
+      <c r="AD43" s="167"/>
+      <c r="AE43" s="167"/>
+      <c r="AF43" s="167"/>
+      <c r="AG43" s="167"/>
+      <c r="AH43" s="167"/>
+      <c r="AI43" s="167"/>
+      <c r="AJ43" s="167"/>
+      <c r="AK43" s="167"/>
+      <c r="AL43" s="167"/>
+      <c r="AM43" s="167"/>
+      <c r="AN43" s="167"/>
+      <c r="AO43" s="168"/>
+      <c r="AP43" s="155"/>
+      <c r="AQ43" s="135"/>
+      <c r="AR43" s="135"/>
+      <c r="AS43" s="135"/>
+      <c r="AT43" s="135"/>
+      <c r="AU43" s="135"/>
+      <c r="AV43" s="136"/>
+      <c r="AW43" s="136"/>
+      <c r="AX43" s="135"/>
+      <c r="AY43" s="135"/>
+      <c r="AZ43" s="135"/>
+      <c r="BA43" s="135"/>
+      <c r="BB43" s="135"/>
+      <c r="BC43" s="135"/>
+      <c r="BD43" s="135"/>
+      <c r="BE43" s="135"/>
+      <c r="BF43" s="135"/>
+      <c r="BG43" s="135"/>
+      <c r="BH43" s="135"/>
+      <c r="BI43" s="135"/>
+      <c r="BJ43" s="135"/>
+      <c r="BK43" s="137"/>
       <c r="BL43" s="9"/>
     </row>
     <row r="44" spans="1:87" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3795,66 +3792,66 @@
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
       <c r="L44" s="12"/>
-      <c r="M44" s="176"/>
-      <c r="N44" s="177"/>
-      <c r="O44" s="177"/>
-      <c r="P44" s="177"/>
-      <c r="Q44" s="177"/>
-      <c r="R44" s="177"/>
-      <c r="S44" s="177"/>
-      <c r="T44" s="177"/>
-      <c r="U44" s="177"/>
-      <c r="V44" s="177"/>
-      <c r="W44" s="177"/>
-      <c r="X44" s="177"/>
-      <c r="Y44" s="177"/>
-      <c r="Z44" s="177"/>
-      <c r="AA44" s="177"/>
-      <c r="AB44" s="177"/>
-      <c r="AC44" s="177"/>
-      <c r="AD44" s="177"/>
-      <c r="AE44" s="177"/>
-      <c r="AF44" s="177"/>
-      <c r="AG44" s="177"/>
-      <c r="AH44" s="177"/>
-      <c r="AI44" s="177"/>
-      <c r="AJ44" s="177"/>
-      <c r="AK44" s="177"/>
-      <c r="AL44" s="177"/>
-      <c r="AM44" s="177"/>
-      <c r="AN44" s="177"/>
-      <c r="AO44" s="178"/>
-      <c r="AP44" s="157"/>
-      <c r="AQ44" s="140" t="str">
+      <c r="M44" s="169"/>
+      <c r="N44" s="170"/>
+      <c r="O44" s="170"/>
+      <c r="P44" s="170"/>
+      <c r="Q44" s="170"/>
+      <c r="R44" s="170"/>
+      <c r="S44" s="170"/>
+      <c r="T44" s="170"/>
+      <c r="U44" s="170"/>
+      <c r="V44" s="170"/>
+      <c r="W44" s="170"/>
+      <c r="X44" s="170"/>
+      <c r="Y44" s="170"/>
+      <c r="Z44" s="170"/>
+      <c r="AA44" s="170"/>
+      <c r="AB44" s="170"/>
+      <c r="AC44" s="170"/>
+      <c r="AD44" s="170"/>
+      <c r="AE44" s="170"/>
+      <c r="AF44" s="170"/>
+      <c r="AG44" s="170"/>
+      <c r="AH44" s="170"/>
+      <c r="AI44" s="170"/>
+      <c r="AJ44" s="170"/>
+      <c r="AK44" s="170"/>
+      <c r="AL44" s="170"/>
+      <c r="AM44" s="170"/>
+      <c r="AN44" s="170"/>
+      <c r="AO44" s="171"/>
+      <c r="AP44" s="156"/>
+      <c r="AQ44" s="139" t="str">
         <f>$AQ$5</f>
         <v>Bagian</v>
       </c>
-      <c r="AR44" s="140"/>
-      <c r="AS44" s="140"/>
-      <c r="AT44" s="140"/>
-      <c r="AU44" s="140"/>
-      <c r="AV44" s="110" t="str">
+      <c r="AR44" s="139"/>
+      <c r="AS44" s="139"/>
+      <c r="AT44" s="139"/>
+      <c r="AU44" s="139"/>
+      <c r="AV44" s="109" t="str">
         <f>$AV$5</f>
         <v xml:space="preserve">:  </v>
       </c>
-      <c r="AW44" s="110" t="str">
+      <c r="AW44" s="109" t="str">
         <f>$AW$5</f>
         <v>SectionName</v>
       </c>
-      <c r="AX44" s="140"/>
-      <c r="AY44" s="140"/>
-      <c r="AZ44" s="140"/>
-      <c r="BA44" s="140"/>
-      <c r="BB44" s="140"/>
-      <c r="BC44" s="140"/>
-      <c r="BD44" s="140"/>
-      <c r="BE44" s="140"/>
-      <c r="BF44" s="140"/>
-      <c r="BG44" s="140"/>
-      <c r="BH44" s="140"/>
-      <c r="BI44" s="140"/>
-      <c r="BJ44" s="140"/>
-      <c r="BK44" s="141"/>
+      <c r="AX44" s="139"/>
+      <c r="AY44" s="139"/>
+      <c r="AZ44" s="139"/>
+      <c r="BA44" s="139"/>
+      <c r="BB44" s="139"/>
+      <c r="BC44" s="139"/>
+      <c r="BD44" s="139"/>
+      <c r="BE44" s="139"/>
+      <c r="BF44" s="139"/>
+      <c r="BG44" s="139"/>
+      <c r="BH44" s="139"/>
+      <c r="BI44" s="139"/>
+      <c r="BJ44" s="139"/>
+      <c r="BK44" s="140"/>
       <c r="BL44" s="13"/>
     </row>
     <row r="45" spans="1:87" ht="6.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3926,96 +3923,96 @@
       <c r="BP46" s="22"/>
     </row>
     <row r="47" spans="1:87" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="167" t="s">
+      <c r="B47" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="C47" s="168"/>
-      <c r="D47" s="168"/>
-      <c r="E47" s="168"/>
-      <c r="F47" s="168"/>
-      <c r="G47" s="168"/>
-      <c r="H47" s="168"/>
-      <c r="I47" s="168"/>
-      <c r="J47" s="168"/>
-      <c r="K47" s="168"/>
-      <c r="L47" s="168"/>
-      <c r="M47" s="168"/>
-      <c r="N47" s="168"/>
-      <c r="O47" s="168"/>
-      <c r="P47" s="168"/>
-      <c r="Q47" s="168"/>
-      <c r="R47" s="168"/>
-      <c r="S47" s="168"/>
-      <c r="T47" s="169"/>
+      <c r="C47" s="188"/>
+      <c r="D47" s="188"/>
+      <c r="E47" s="188"/>
+      <c r="F47" s="188"/>
+      <c r="G47" s="188"/>
+      <c r="H47" s="188"/>
+      <c r="I47" s="188"/>
+      <c r="J47" s="188"/>
+      <c r="K47" s="188"/>
+      <c r="L47" s="188"/>
+      <c r="M47" s="188"/>
+      <c r="N47" s="188"/>
+      <c r="O47" s="188"/>
+      <c r="P47" s="188"/>
+      <c r="Q47" s="188"/>
+      <c r="R47" s="188"/>
+      <c r="S47" s="188"/>
+      <c r="T47" s="189"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="167" t="s">
+      <c r="V47" s="187" t="s">
         <v>19</v>
       </c>
-      <c r="W47" s="168"/>
-      <c r="X47" s="168"/>
-      <c r="Y47" s="168"/>
-      <c r="Z47" s="168"/>
-      <c r="AA47" s="168"/>
-      <c r="AB47" s="168"/>
-      <c r="AC47" s="168"/>
-      <c r="AD47" s="168"/>
-      <c r="AE47" s="168"/>
-      <c r="AF47" s="168"/>
-      <c r="AG47" s="168"/>
-      <c r="AH47" s="168"/>
-      <c r="AI47" s="168"/>
-      <c r="AJ47" s="168"/>
-      <c r="AK47" s="168"/>
-      <c r="AL47" s="168"/>
-      <c r="AM47" s="168"/>
-      <c r="AN47" s="168"/>
-      <c r="AO47" s="169"/>
+      <c r="W47" s="188"/>
+      <c r="X47" s="188"/>
+      <c r="Y47" s="188"/>
+      <c r="Z47" s="188"/>
+      <c r="AA47" s="188"/>
+      <c r="AB47" s="188"/>
+      <c r="AC47" s="188"/>
+      <c r="AD47" s="188"/>
+      <c r="AE47" s="188"/>
+      <c r="AF47" s="188"/>
+      <c r="AG47" s="188"/>
+      <c r="AH47" s="188"/>
+      <c r="AI47" s="188"/>
+      <c r="AJ47" s="188"/>
+      <c r="AK47" s="188"/>
+      <c r="AL47" s="188"/>
+      <c r="AM47" s="188"/>
+      <c r="AN47" s="188"/>
+      <c r="AO47" s="189"/>
       <c r="AP47" s="1"/>
-      <c r="AQ47" s="167" t="s">
+      <c r="AQ47" s="187" t="s">
         <v>20</v>
       </c>
-      <c r="AR47" s="168"/>
-      <c r="AS47" s="168"/>
-      <c r="AT47" s="168"/>
-      <c r="AU47" s="168"/>
-      <c r="AV47" s="168"/>
-      <c r="AW47" s="168"/>
-      <c r="AX47" s="168"/>
-      <c r="AY47" s="168"/>
-      <c r="AZ47" s="168"/>
-      <c r="BA47" s="168"/>
-      <c r="BB47" s="168"/>
-      <c r="BC47" s="168"/>
-      <c r="BD47" s="168"/>
-      <c r="BE47" s="168"/>
-      <c r="BF47" s="168"/>
-      <c r="BG47" s="168"/>
-      <c r="BH47" s="168"/>
-      <c r="BI47" s="168"/>
-      <c r="BJ47" s="168"/>
-      <c r="BK47" s="169"/>
+      <c r="AR47" s="188"/>
+      <c r="AS47" s="188"/>
+      <c r="AT47" s="188"/>
+      <c r="AU47" s="188"/>
+      <c r="AV47" s="188"/>
+      <c r="AW47" s="188"/>
+      <c r="AX47" s="188"/>
+      <c r="AY47" s="188"/>
+      <c r="AZ47" s="188"/>
+      <c r="BA47" s="188"/>
+      <c r="BB47" s="188"/>
+      <c r="BC47" s="188"/>
+      <c r="BD47" s="188"/>
+      <c r="BE47" s="188"/>
+      <c r="BF47" s="188"/>
+      <c r="BG47" s="188"/>
+      <c r="BH47" s="188"/>
+      <c r="BI47" s="188"/>
+      <c r="BJ47" s="188"/>
+      <c r="BK47" s="189"/>
       <c r="BN47" s="22"/>
       <c r="BO47" s="23"/>
       <c r="BP47" s="22"/>
     </row>
     <row r="48" spans="1:87" ht="14.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="125"/>
+      <c r="B48" s="124"/>
       <c r="C48" s="33"/>
-      <c r="D48" s="129"/>
-      <c r="E48" s="113"/>
-      <c r="F48" s="113"/>
-      <c r="G48" s="113"/>
-      <c r="H48" s="113"/>
-      <c r="I48" s="113"/>
-      <c r="J48" s="113"/>
-      <c r="K48" s="113"/>
-      <c r="L48" s="113"/>
-      <c r="M48" s="113"/>
-      <c r="N48" s="113"/>
-      <c r="O48" s="113"/>
-      <c r="P48" s="113"/>
-      <c r="Q48" s="113"/>
-      <c r="R48" s="113"/>
+      <c r="D48" s="128"/>
+      <c r="E48" s="112"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="112"/>
+      <c r="H48" s="112"/>
+      <c r="I48" s="112"/>
+      <c r="J48" s="112"/>
+      <c r="K48" s="112"/>
+      <c r="L48" s="112"/>
+      <c r="M48" s="112"/>
+      <c r="N48" s="112"/>
+      <c r="O48" s="112"/>
+      <c r="P48" s="112"/>
+      <c r="Q48" s="112"/>
+      <c r="R48" s="112"/>
       <c r="S48" s="66"/>
       <c r="T48" s="67"/>
       <c r="V48" s="68"/>
@@ -4041,35 +4038,35 @@
       <c r="BI48" s="59"/>
       <c r="BJ48" s="56"/>
       <c r="BK48" s="71"/>
-      <c r="BO48" s="160"/>
-      <c r="BP48" s="160"/>
-      <c r="BQ48" s="160"/>
-      <c r="BR48" s="160"/>
-      <c r="BS48" s="160"/>
-      <c r="BT48" s="160"/>
-      <c r="BU48" s="160"/>
-      <c r="BV48" s="160"/>
-      <c r="BW48" s="160"/>
-      <c r="BX48" s="160"/>
-      <c r="BY48" s="160"/>
-      <c r="BZ48" s="160"/>
-      <c r="CA48" s="160"/>
-      <c r="CB48" s="160"/>
-      <c r="CC48" s="160"/>
-      <c r="CD48" s="160"/>
-      <c r="CE48" s="160"/>
-      <c r="CF48" s="160"/>
-      <c r="CG48" s="160"/>
-      <c r="CH48" s="160"/>
-      <c r="CI48" s="160"/>
+      <c r="BO48" s="190"/>
+      <c r="BP48" s="190"/>
+      <c r="BQ48" s="190"/>
+      <c r="BR48" s="190"/>
+      <c r="BS48" s="190"/>
+      <c r="BT48" s="190"/>
+      <c r="BU48" s="190"/>
+      <c r="BV48" s="190"/>
+      <c r="BW48" s="190"/>
+      <c r="BX48" s="190"/>
+      <c r="BY48" s="190"/>
+      <c r="BZ48" s="190"/>
+      <c r="CA48" s="190"/>
+      <c r="CB48" s="190"/>
+      <c r="CC48" s="190"/>
+      <c r="CD48" s="190"/>
+      <c r="CE48" s="190"/>
+      <c r="CF48" s="190"/>
+      <c r="CG48" s="190"/>
+      <c r="CH48" s="190"/>
+      <c r="CI48" s="190"/>
     </row>
     <row r="49" spans="2:84" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="153" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="117"/>
+      <c r="B49" s="152" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="116"/>
       <c r="D49" s="55"/>
-      <c r="E49" s="113"/>
+      <c r="E49" s="112"/>
       <c r="F49" s="56"/>
       <c r="G49" s="56"/>
       <c r="H49" s="56"/>
@@ -4079,17 +4076,17 @@
       <c r="L49" s="56"/>
       <c r="M49" s="56"/>
       <c r="N49" s="56"/>
-      <c r="O49" s="113"/>
-      <c r="P49" s="113"/>
-      <c r="Q49" s="113"/>
-      <c r="R49" s="113"/>
+      <c r="O49" s="112"/>
+      <c r="P49" s="112"/>
+      <c r="Q49" s="112"/>
+      <c r="R49" s="112"/>
       <c r="S49" s="66"/>
       <c r="T49" s="67"/>
       <c r="V49" s="72">
         <v>1</v>
       </c>
       <c r="W49" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="X49" s="29"/>
       <c r="AO49" s="8"/>
@@ -4121,9 +4118,9 @@
       <c r="BP49" s="1"/>
     </row>
     <row r="50" spans="2:84" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="126"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="130"/>
+      <c r="B50" s="125"/>
+      <c r="C50" s="116"/>
+      <c r="D50" s="129"/>
       <c r="E50" s="97"/>
       <c r="F50" s="97"/>
       <c r="G50" s="97"/>
@@ -4172,9 +4169,9 @@
     </row>
     <row r="51" spans="2:84" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="54"/>
-      <c r="C51" s="117"/>
+      <c r="C51" s="116"/>
       <c r="D51" s="29"/>
-      <c r="E51" s="127"/>
+      <c r="E51" s="126"/>
       <c r="F51" s="97"/>
       <c r="G51" s="97"/>
       <c r="H51" s="97"/>
@@ -4184,7 +4181,7 @@
       <c r="L51" s="97"/>
       <c r="M51" s="97"/>
       <c r="N51" s="97"/>
-      <c r="O51" s="127"/>
+      <c r="O51" s="126"/>
       <c r="P51" s="97"/>
       <c r="Q51" s="97"/>
       <c r="R51" s="97"/>
@@ -4225,7 +4222,7 @@
       <c r="B52" s="78"/>
       <c r="C52" s="27"/>
       <c r="D52" s="29"/>
-      <c r="E52" s="127"/>
+      <c r="E52" s="126"/>
       <c r="F52" s="97"/>
       <c r="G52" s="97"/>
       <c r="H52" s="97"/>
@@ -4235,7 +4232,7 @@
       <c r="L52" s="97"/>
       <c r="M52" s="97"/>
       <c r="N52" s="97"/>
-      <c r="O52" s="127"/>
+      <c r="O52" s="126"/>
       <c r="P52" s="97"/>
       <c r="Q52" s="97"/>
       <c r="R52" s="97"/>
@@ -4249,7 +4246,7 @@
       <c r="AO52" s="8"/>
       <c r="AQ52" s="77"/>
       <c r="AR52" s="73" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS52" s="52"/>
       <c r="AT52" s="52"/>
@@ -4274,7 +4271,7 @@
       <c r="B53" s="60"/>
       <c r="C53" s="29"/>
       <c r="D53" s="29"/>
-      <c r="E53" s="127"/>
+      <c r="E53" s="126"/>
       <c r="F53" s="97"/>
       <c r="G53" s="97"/>
       <c r="H53" s="97"/>
@@ -4284,7 +4281,7 @@
       <c r="L53" s="97"/>
       <c r="M53" s="97"/>
       <c r="N53" s="97"/>
-      <c r="O53" s="127"/>
+      <c r="O53" s="126"/>
       <c r="P53" s="97"/>
       <c r="Q53" s="97"/>
       <c r="R53" s="97"/>
@@ -4321,7 +4318,7 @@
       <c r="B54" s="60"/>
       <c r="C54" s="55"/>
       <c r="D54" s="29"/>
-      <c r="E54" s="127"/>
+      <c r="E54" s="126"/>
       <c r="F54" s="97"/>
       <c r="G54" s="97"/>
       <c r="H54" s="97"/>
@@ -4331,7 +4328,7 @@
       <c r="L54" s="97"/>
       <c r="M54" s="97"/>
       <c r="N54" s="97"/>
-      <c r="O54" s="127"/>
+      <c r="O54" s="126"/>
       <c r="P54" s="97"/>
       <c r="Q54" s="97"/>
       <c r="R54" s="97"/>
@@ -4370,7 +4367,7 @@
       <c r="B55" s="60"/>
       <c r="C55" s="57"/>
       <c r="D55" s="29"/>
-      <c r="E55" s="127"/>
+      <c r="E55" s="126"/>
       <c r="F55" s="97"/>
       <c r="G55" s="97"/>
       <c r="H55" s="97"/>
@@ -4380,7 +4377,7 @@
       <c r="L55" s="97"/>
       <c r="M55" s="97"/>
       <c r="N55" s="97"/>
-      <c r="O55" s="127"/>
+      <c r="O55" s="126"/>
       <c r="P55" s="97"/>
       <c r="Q55" s="97"/>
       <c r="R55" s="97"/>
@@ -4416,7 +4413,7 @@
       <c r="B56" s="78"/>
       <c r="C56" s="57"/>
       <c r="D56" s="29"/>
-      <c r="E56" s="127"/>
+      <c r="E56" s="126"/>
       <c r="F56" s="97"/>
       <c r="G56" s="97"/>
       <c r="H56" s="97"/>
@@ -4426,7 +4423,7 @@
       <c r="L56" s="97"/>
       <c r="M56" s="97"/>
       <c r="N56" s="97"/>
-      <c r="O56" s="127"/>
+      <c r="O56" s="126"/>
       <c r="P56" s="97"/>
       <c r="Q56" s="97"/>
       <c r="R56" s="97"/>
@@ -4438,7 +4435,7 @@
         <v>4</v>
       </c>
       <c r="AR56" s="57" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AT56" s="82"/>
       <c r="AU56" s="82"/>
@@ -4462,7 +4459,7 @@
       <c r="B57" s="78"/>
       <c r="C57" s="29"/>
       <c r="D57" s="29"/>
-      <c r="E57" s="127"/>
+      <c r="E57" s="126"/>
       <c r="F57" s="97"/>
       <c r="G57" s="97"/>
       <c r="H57" s="97"/>
@@ -4472,7 +4469,7 @@
       <c r="L57" s="97"/>
       <c r="M57" s="97"/>
       <c r="N57" s="97"/>
-      <c r="O57" s="127"/>
+      <c r="O57" s="126"/>
       <c r="P57" s="97"/>
       <c r="Q57" s="97"/>
       <c r="R57" s="97"/>
@@ -4504,7 +4501,7 @@
       <c r="B58" s="78"/>
       <c r="C58" s="55"/>
       <c r="D58" s="29"/>
-      <c r="E58" s="127"/>
+      <c r="E58" s="126"/>
       <c r="F58" s="97"/>
       <c r="G58" s="97"/>
       <c r="H58" s="97"/>
@@ -4514,7 +4511,7 @@
       <c r="L58" s="97"/>
       <c r="M58" s="97"/>
       <c r="N58" s="97"/>
-      <c r="O58" s="127"/>
+      <c r="O58" s="126"/>
       <c r="P58" s="97"/>
       <c r="Q58" s="97"/>
       <c r="R58" s="97"/>
@@ -4546,8 +4543,8 @@
       <c r="B59" s="78"/>
       <c r="C59" s="55"/>
       <c r="D59" s="55"/>
-      <c r="E59" s="127"/>
-      <c r="F59" s="128"/>
+      <c r="E59" s="126"/>
+      <c r="F59" s="127"/>
       <c r="G59" s="97"/>
       <c r="H59" s="97"/>
       <c r="I59" s="97"/>
@@ -4556,7 +4553,7 @@
       <c r="L59" s="97"/>
       <c r="M59" s="97"/>
       <c r="N59" s="97"/>
-      <c r="O59" s="127"/>
+      <c r="O59" s="126"/>
       <c r="P59" s="97"/>
       <c r="Q59" s="97"/>
       <c r="R59" s="97"/>
@@ -4584,26 +4581,26 @@
       <c r="BI59" s="82"/>
       <c r="BK59" s="8"/>
       <c r="BO59" s="1"/>
-      <c r="BP59" s="160"/>
-      <c r="BQ59" s="160"/>
-      <c r="BR59" s="160"/>
-      <c r="BS59" s="160"/>
-      <c r="BT59" s="160"/>
-      <c r="BU59" s="160"/>
-      <c r="BV59" s="160"/>
-      <c r="BW59" s="160"/>
-      <c r="BX59" s="160"/>
-      <c r="BY59" s="160"/>
-      <c r="BZ59" s="160"/>
-      <c r="CA59" s="160"/>
-      <c r="CB59" s="160"/>
-      <c r="CC59" s="160"/>
-      <c r="CD59" s="160"/>
-      <c r="CE59" s="160"/>
-      <c r="CF59" s="160"/>
+      <c r="BP59" s="190"/>
+      <c r="BQ59" s="190"/>
+      <c r="BR59" s="190"/>
+      <c r="BS59" s="190"/>
+      <c r="BT59" s="190"/>
+      <c r="BU59" s="190"/>
+      <c r="BV59" s="190"/>
+      <c r="BW59" s="190"/>
+      <c r="BX59" s="190"/>
+      <c r="BY59" s="190"/>
+      <c r="BZ59" s="190"/>
+      <c r="CA59" s="190"/>
+      <c r="CB59" s="190"/>
+      <c r="CC59" s="190"/>
+      <c r="CD59" s="190"/>
+      <c r="CE59" s="190"/>
+      <c r="CF59" s="190"/>
     </row>
     <row r="60" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="119"/>
+      <c r="B60" s="118"/>
       <c r="C60" s="88"/>
       <c r="D60" s="56"/>
       <c r="E60" s="56"/>
@@ -4702,28 +4699,28 @@
       <c r="R62" s="48"/>
       <c r="S62" s="48"/>
       <c r="T62" s="87"/>
-      <c r="V62" s="161" t="s">
+      <c r="V62" s="172" t="s">
         <v>27</v>
       </c>
-      <c r="W62" s="162"/>
-      <c r="X62" s="162"/>
-      <c r="Y62" s="162"/>
-      <c r="Z62" s="162"/>
-      <c r="AA62" s="162"/>
-      <c r="AB62" s="162"/>
-      <c r="AC62" s="162"/>
-      <c r="AD62" s="162"/>
-      <c r="AE62" s="162"/>
-      <c r="AF62" s="162"/>
-      <c r="AG62" s="162"/>
-      <c r="AH62" s="162"/>
-      <c r="AI62" s="162"/>
-      <c r="AJ62" s="162"/>
-      <c r="AK62" s="162"/>
-      <c r="AL62" s="162"/>
-      <c r="AM62" s="162"/>
-      <c r="AN62" s="162"/>
-      <c r="AO62" s="163"/>
+      <c r="W62" s="173"/>
+      <c r="X62" s="173"/>
+      <c r="Y62" s="173"/>
+      <c r="Z62" s="173"/>
+      <c r="AA62" s="173"/>
+      <c r="AB62" s="173"/>
+      <c r="AC62" s="173"/>
+      <c r="AD62" s="173"/>
+      <c r="AE62" s="173"/>
+      <c r="AF62" s="173"/>
+      <c r="AG62" s="173"/>
+      <c r="AH62" s="173"/>
+      <c r="AI62" s="173"/>
+      <c r="AJ62" s="173"/>
+      <c r="AK62" s="173"/>
+      <c r="AL62" s="173"/>
+      <c r="AM62" s="173"/>
+      <c r="AN62" s="173"/>
+      <c r="AO62" s="174"/>
       <c r="AP62" s="38"/>
       <c r="AS62" s="82"/>
       <c r="AT62" s="82"/>
@@ -4764,7 +4761,7 @@
       <c r="R63" s="48"/>
       <c r="S63" s="48"/>
       <c r="T63" s="87"/>
-      <c r="V63" s="107"/>
+      <c r="V63" s="106"/>
       <c r="W63" s="90"/>
       <c r="X63" s="31"/>
       <c r="AO63" s="8"/>
@@ -4808,7 +4805,7 @@
       <c r="S64" s="1"/>
       <c r="T64" s="34"/>
       <c r="U64" s="38"/>
-      <c r="V64" s="118">
+      <c r="V64" s="117">
         <v>1</v>
       </c>
       <c r="W64" s="29"/>
@@ -4840,7 +4837,7 @@
       <c r="L65" s="48"/>
       <c r="T65" s="8"/>
       <c r="U65" s="38"/>
-      <c r="V65" s="118">
+      <c r="V65" s="117">
         <v>2</v>
       </c>
       <c r="W65" s="55"/>
@@ -4887,7 +4884,7 @@
       <c r="S66" s="1"/>
       <c r="T66" s="34"/>
       <c r="U66" s="38"/>
-      <c r="V66" s="118">
+      <c r="V66" s="117">
         <v>3</v>
       </c>
       <c r="W66" s="55"/>
@@ -4935,7 +4932,7 @@
       <c r="S67" s="1"/>
       <c r="T67" s="1"/>
       <c r="U67" s="38"/>
-      <c r="V67" s="118">
+      <c r="V67" s="117">
         <v>4</v>
       </c>
       <c r="W67" s="55"/>
@@ -4983,7 +4980,7 @@
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
       <c r="U68" s="38"/>
-      <c r="V68" s="118">
+      <c r="V68" s="117">
         <v>5</v>
       </c>
       <c r="W68" s="55"/>
@@ -5032,7 +5029,7 @@
       <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="38"/>
-      <c r="V69" s="114"/>
+      <c r="V69" s="113"/>
       <c r="W69" s="31"/>
       <c r="X69" s="31"/>
       <c r="AO69" s="8"/>
@@ -5062,7 +5059,7 @@
       <c r="B70" s="7"/>
       <c r="T70" s="8"/>
       <c r="U70" s="38"/>
-      <c r="V70" s="117"/>
+      <c r="V70" s="116"/>
       <c r="W70" s="29"/>
       <c r="AO70" s="8"/>
       <c r="AP70" s="38"/>
@@ -5072,30 +5069,30 @@
       <c r="B71" s="7"/>
       <c r="T71" s="8"/>
       <c r="U71" s="38"/>
-      <c r="V71" s="114"/>
+      <c r="V71" s="113"/>
       <c r="W71" s="56"/>
       <c r="X71" s="56"/>
       <c r="AO71" s="8"/>
       <c r="AP71" s="8"/>
       <c r="BK71" s="8"/>
-      <c r="BO71" s="160"/>
-      <c r="BP71" s="160"/>
-      <c r="BQ71" s="160"/>
-      <c r="BR71" s="160"/>
-      <c r="BS71" s="160"/>
-      <c r="BT71" s="160"/>
-      <c r="BU71" s="160"/>
-      <c r="BV71" s="160"/>
-      <c r="BW71" s="160"/>
-      <c r="BX71" s="160"/>
-      <c r="BY71" s="160"/>
-      <c r="BZ71" s="160"/>
-      <c r="CA71" s="160"/>
-      <c r="CB71" s="160"/>
-      <c r="CC71" s="160"/>
-      <c r="CD71" s="160"/>
-      <c r="CE71" s="160"/>
-      <c r="CF71" s="160"/>
+      <c r="BO71" s="190"/>
+      <c r="BP71" s="190"/>
+      <c r="BQ71" s="190"/>
+      <c r="BR71" s="190"/>
+      <c r="BS71" s="190"/>
+      <c r="BT71" s="190"/>
+      <c r="BU71" s="190"/>
+      <c r="BV71" s="190"/>
+      <c r="BW71" s="190"/>
+      <c r="BX71" s="190"/>
+      <c r="BY71" s="190"/>
+      <c r="BZ71" s="190"/>
+      <c r="CA71" s="190"/>
+      <c r="CB71" s="190"/>
+      <c r="CC71" s="190"/>
+      <c r="CD71" s="190"/>
+      <c r="CE71" s="190"/>
+      <c r="CF71" s="190"/>
     </row>
     <row r="72" spans="2:84" x14ac:dyDescent="0.2">
       <c r="B72" s="7"/>
@@ -5140,98 +5137,98 @@
       <c r="BK76" s="12"/>
     </row>
     <row r="77" spans="2:84" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="161" t="s">
+      <c r="B77" s="172" t="s">
         <v>28</v>
       </c>
-      <c r="C77" s="162"/>
-      <c r="D77" s="162"/>
-      <c r="E77" s="162"/>
-      <c r="F77" s="162"/>
-      <c r="G77" s="162"/>
-      <c r="H77" s="162"/>
-      <c r="I77" s="162"/>
-      <c r="J77" s="162"/>
-      <c r="K77" s="162"/>
-      <c r="L77" s="162"/>
-      <c r="M77" s="162"/>
-      <c r="N77" s="162"/>
-      <c r="O77" s="162"/>
-      <c r="P77" s="162"/>
-      <c r="Q77" s="162"/>
-      <c r="R77" s="162"/>
-      <c r="S77" s="162"/>
-      <c r="T77" s="162"/>
-      <c r="U77" s="162"/>
-      <c r="V77" s="162"/>
-      <c r="W77" s="162"/>
-      <c r="X77" s="162"/>
-      <c r="Y77" s="162"/>
-      <c r="Z77" s="162"/>
-      <c r="AA77" s="162"/>
-      <c r="AB77" s="162"/>
-      <c r="AC77" s="162"/>
-      <c r="AD77" s="162"/>
-      <c r="AE77" s="162"/>
-      <c r="AF77" s="162"/>
-      <c r="AG77" s="162"/>
-      <c r="AH77" s="162"/>
-      <c r="AI77" s="162"/>
-      <c r="AJ77" s="162"/>
-      <c r="AK77" s="162"/>
-      <c r="AL77" s="162"/>
-      <c r="AM77" s="162"/>
-      <c r="AN77" s="162"/>
-      <c r="AO77" s="162"/>
-      <c r="AP77" s="162"/>
-      <c r="AQ77" s="162"/>
-      <c r="AR77" s="162"/>
-      <c r="AS77" s="162"/>
-      <c r="AT77" s="162"/>
-      <c r="AU77" s="162"/>
-      <c r="AV77" s="162"/>
-      <c r="AW77" s="162"/>
-      <c r="AX77" s="162"/>
-      <c r="AY77" s="162"/>
-      <c r="AZ77" s="162"/>
-      <c r="BA77" s="162"/>
-      <c r="BB77" s="162"/>
-      <c r="BC77" s="162"/>
-      <c r="BD77" s="162"/>
-      <c r="BE77" s="162"/>
-      <c r="BF77" s="162"/>
-      <c r="BG77" s="162"/>
-      <c r="BH77" s="162"/>
-      <c r="BI77" s="162"/>
-      <c r="BJ77" s="162"/>
-      <c r="BK77" s="163"/>
+      <c r="C77" s="173"/>
+      <c r="D77" s="173"/>
+      <c r="E77" s="173"/>
+      <c r="F77" s="173"/>
+      <c r="G77" s="173"/>
+      <c r="H77" s="173"/>
+      <c r="I77" s="173"/>
+      <c r="J77" s="173"/>
+      <c r="K77" s="173"/>
+      <c r="L77" s="173"/>
+      <c r="M77" s="173"/>
+      <c r="N77" s="173"/>
+      <c r="O77" s="173"/>
+      <c r="P77" s="173"/>
+      <c r="Q77" s="173"/>
+      <c r="R77" s="173"/>
+      <c r="S77" s="173"/>
+      <c r="T77" s="173"/>
+      <c r="U77" s="173"/>
+      <c r="V77" s="173"/>
+      <c r="W77" s="173"/>
+      <c r="X77" s="173"/>
+      <c r="Y77" s="173"/>
+      <c r="Z77" s="173"/>
+      <c r="AA77" s="173"/>
+      <c r="AB77" s="173"/>
+      <c r="AC77" s="173"/>
+      <c r="AD77" s="173"/>
+      <c r="AE77" s="173"/>
+      <c r="AF77" s="173"/>
+      <c r="AG77" s="173"/>
+      <c r="AH77" s="173"/>
+      <c r="AI77" s="173"/>
+      <c r="AJ77" s="173"/>
+      <c r="AK77" s="173"/>
+      <c r="AL77" s="173"/>
+      <c r="AM77" s="173"/>
+      <c r="AN77" s="173"/>
+      <c r="AO77" s="173"/>
+      <c r="AP77" s="173"/>
+      <c r="AQ77" s="173"/>
+      <c r="AR77" s="173"/>
+      <c r="AS77" s="173"/>
+      <c r="AT77" s="173"/>
+      <c r="AU77" s="173"/>
+      <c r="AV77" s="173"/>
+      <c r="AW77" s="173"/>
+      <c r="AX77" s="173"/>
+      <c r="AY77" s="173"/>
+      <c r="AZ77" s="173"/>
+      <c r="BA77" s="173"/>
+      <c r="BB77" s="173"/>
+      <c r="BC77" s="173"/>
+      <c r="BD77" s="173"/>
+      <c r="BE77" s="173"/>
+      <c r="BF77" s="173"/>
+      <c r="BG77" s="173"/>
+      <c r="BH77" s="173"/>
+      <c r="BI77" s="173"/>
+      <c r="BJ77" s="173"/>
+      <c r="BK77" s="174"/>
     </row>
     <row r="78" spans="2:84" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="164" t="s">
+      <c r="B78" s="184" t="s">
         <v>29</v>
       </c>
-      <c r="C78" s="165"/>
-      <c r="D78" s="165"/>
-      <c r="E78" s="165"/>
-      <c r="F78" s="165"/>
-      <c r="G78" s="165"/>
-      <c r="H78" s="165"/>
-      <c r="I78" s="165"/>
-      <c r="J78" s="165"/>
-      <c r="K78" s="165"/>
-      <c r="L78" s="165"/>
-      <c r="M78" s="165"/>
-      <c r="N78" s="165"/>
-      <c r="O78" s="165"/>
-      <c r="P78" s="165"/>
-      <c r="Q78" s="165"/>
-      <c r="R78" s="165"/>
-      <c r="S78" s="165"/>
-      <c r="T78" s="165"/>
+      <c r="C78" s="185"/>
+      <c r="D78" s="185"/>
+      <c r="E78" s="185"/>
+      <c r="F78" s="185"/>
+      <c r="G78" s="185"/>
+      <c r="H78" s="185"/>
+      <c r="I78" s="185"/>
+      <c r="J78" s="185"/>
+      <c r="K78" s="185"/>
+      <c r="L78" s="185"/>
+      <c r="M78" s="185"/>
+      <c r="N78" s="185"/>
+      <c r="O78" s="185"/>
+      <c r="P78" s="185"/>
+      <c r="Q78" s="185"/>
+      <c r="R78" s="185"/>
+      <c r="S78" s="185"/>
+      <c r="T78" s="185"/>
       <c r="U78" s="4"/>
       <c r="V78" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="W78" s="108"/>
+      <c r="W78" s="107"/>
       <c r="AQ78" s="4"/>
       <c r="BK78" s="5"/>
     </row>
@@ -5258,18 +5255,18 @@
       <c r="S79" s="48"/>
       <c r="T79" s="48"/>
       <c r="V79" s="48" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="W79" s="48"/>
       <c r="AQ79" s="95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AR79" s="96"/>
       <c r="BK79" s="8"/>
     </row>
     <row r="80" spans="2:84" x14ac:dyDescent="0.25">
       <c r="B80" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D80" s="97"/>
       <c r="E80" s="97"/>
@@ -5297,12 +5294,10 @@
       <c r="BK80" s="8"/>
     </row>
     <row r="81" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B81" s="99" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="33" t="s">
-        <v>45</v>
-      </c>
+      <c r="B81" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="56"/>
       <c r="D81" s="56"/>
       <c r="E81" s="97"/>
       <c r="F81" s="97"/>
@@ -5321,12 +5316,10 @@
       <c r="S81" s="97"/>
       <c r="T81" s="97"/>
       <c r="U81" s="56"/>
-      <c r="V81" s="121" t="s">
-        <v>53</v>
-      </c>
-      <c r="W81" s="120" t="s">
-        <v>54</v>
-      </c>
+      <c r="V81" s="119" t="s">
+        <v>51</v>
+      </c>
+      <c r="W81" s="56"/>
       <c r="X81" s="56"/>
       <c r="Y81" s="56"/>
       <c r="Z81" s="56"/>
@@ -5346,12 +5339,10 @@
       <c r="AN81" s="56"/>
       <c r="AO81" s="56"/>
       <c r="AP81" s="56"/>
-      <c r="AQ81" s="121" t="s">
-        <v>53</v>
-      </c>
-      <c r="AR81" s="150" t="s">
-        <v>46</v>
-      </c>
+      <c r="AQ81" s="116" t="s">
+        <v>52</v>
+      </c>
+      <c r="AR81" s="149"/>
       <c r="AS81" s="56"/>
       <c r="AT81" s="56"/>
       <c r="AU81" s="56"/>
@@ -5360,12 +5351,8 @@
       <c r="BK81" s="8"/>
     </row>
     <row r="82" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B82" s="153" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="33" t="s">
-        <v>46</v>
-      </c>
+      <c r="B82" s="125"/>
+      <c r="C82" s="33"/>
       <c r="D82" s="97"/>
       <c r="E82" s="97"/>
       <c r="F82" s="97"/>
@@ -5384,12 +5371,8 @@
       <c r="S82" s="97"/>
       <c r="T82" s="97"/>
       <c r="U82" s="56"/>
-      <c r="V82" s="121" t="s">
-        <v>55</v>
-      </c>
-      <c r="W82" s="159" t="s">
-        <v>46</v>
-      </c>
+      <c r="V82" s="117"/>
+      <c r="W82" s="158"/>
       <c r="X82" s="56"/>
       <c r="Y82" s="56"/>
       <c r="Z82" s="56"/>
@@ -5409,12 +5392,8 @@
       <c r="AN82" s="56"/>
       <c r="AO82" s="56"/>
       <c r="AP82" s="56"/>
-      <c r="AQ82" s="121" t="s">
-        <v>55</v>
-      </c>
-      <c r="AR82" s="150" t="s">
-        <v>46</v>
-      </c>
+      <c r="AQ82" s="117"/>
+      <c r="AR82" s="149"/>
       <c r="AS82" s="56"/>
       <c r="AT82" s="56"/>
       <c r="AU82" s="56"/>
@@ -5423,12 +5402,8 @@
       <c r="BK82" s="8"/>
     </row>
     <row r="83" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B83" s="99" t="s">
-        <v>56</v>
-      </c>
-      <c r="C83" s="124" t="s">
-        <v>46</v>
-      </c>
+      <c r="B83" s="191"/>
+      <c r="C83" s="123"/>
       <c r="D83" s="97"/>
       <c r="E83" s="97"/>
       <c r="F83" s="97"/>
@@ -5447,12 +5422,8 @@
       <c r="S83" s="97"/>
       <c r="T83" s="97"/>
       <c r="U83" s="56"/>
-      <c r="V83" s="120" t="s">
-        <v>56</v>
-      </c>
-      <c r="W83" s="159" t="s">
-        <v>46</v>
-      </c>
+      <c r="V83" s="192"/>
+      <c r="W83" s="158"/>
       <c r="X83" s="56"/>
       <c r="Y83" s="56"/>
       <c r="Z83" s="56"/>
@@ -5472,12 +5443,8 @@
       <c r="AN83" s="56"/>
       <c r="AO83" s="56"/>
       <c r="AP83" s="56"/>
-      <c r="AQ83" s="120" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR83" s="150" t="s">
-        <v>46</v>
-      </c>
+      <c r="AQ83" s="192"/>
+      <c r="AR83" s="149"/>
       <c r="AS83" s="56"/>
       <c r="AT83" s="56"/>
       <c r="AU83" s="56"/>
@@ -5486,8 +5453,8 @@
       <c r="BK83" s="8"/>
     </row>
     <row r="84" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B84" s="99"/>
-      <c r="C84" s="124"/>
+      <c r="B84" s="191"/>
+      <c r="C84" s="123"/>
       <c r="D84" s="97"/>
       <c r="E84" s="97"/>
       <c r="F84" s="97"/>
@@ -5506,7 +5473,7 @@
       <c r="S84" s="97"/>
       <c r="T84" s="97"/>
       <c r="U84" s="56"/>
-      <c r="V84" s="120"/>
+      <c r="V84" s="119"/>
       <c r="W84" s="56"/>
       <c r="X84" s="56"/>
       <c r="Y84" s="56"/>
@@ -5527,7 +5494,7 @@
       <c r="AN84" s="56"/>
       <c r="AO84" s="56"/>
       <c r="AP84" s="56"/>
-      <c r="AQ84" s="120"/>
+      <c r="AQ84" s="119"/>
       <c r="AR84" s="56"/>
       <c r="AS84" s="56"/>
       <c r="AT84" s="56"/>
@@ -5537,8 +5504,8 @@
       <c r="BK84" s="8"/>
     </row>
     <row r="85" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B85" s="151"/>
-      <c r="C85" s="124"/>
+      <c r="B85" s="150"/>
+      <c r="C85" s="123"/>
       <c r="D85" s="97"/>
       <c r="E85" s="97"/>
       <c r="F85" s="97"/>
@@ -5557,7 +5524,7 @@
       <c r="S85" s="97"/>
       <c r="T85" s="97"/>
       <c r="U85" s="56"/>
-      <c r="V85" s="121"/>
+      <c r="V85" s="120"/>
       <c r="W85" s="33"/>
       <c r="X85" s="56"/>
       <c r="Y85" s="56"/>
@@ -5585,12 +5552,12 @@
       <c r="AU85" s="56"/>
       <c r="AV85" s="56"/>
       <c r="AW85" s="56"/>
-      <c r="AX85" s="101"/>
+      <c r="AX85" s="100"/>
       <c r="BK85" s="8"/>
     </row>
     <row r="86" spans="2:63" x14ac:dyDescent="0.25">
-      <c r="B86" s="100"/>
-      <c r="C86" s="124"/>
+      <c r="B86" s="99"/>
+      <c r="C86" s="123"/>
       <c r="D86" s="97"/>
       <c r="E86" s="97"/>
       <c r="F86" s="97"/>
@@ -5609,7 +5576,7 @@
       <c r="S86" s="97"/>
       <c r="T86" s="97"/>
       <c r="U86" s="56"/>
-      <c r="V86" s="121"/>
+      <c r="V86" s="120"/>
       <c r="W86" s="33"/>
       <c r="X86" s="56"/>
       <c r="Y86" s="56"/>
@@ -5630,60 +5597,60 @@
       <c r="AN86" s="56"/>
       <c r="AO86" s="56"/>
       <c r="AP86" s="50"/>
-      <c r="AQ86" s="152"/>
+      <c r="AQ86" s="151"/>
       <c r="AR86" s="56"/>
       <c r="AS86" s="56"/>
       <c r="AT86" s="56"/>
       <c r="AU86" s="56"/>
       <c r="AV86" s="56"/>
       <c r="AW86" s="56"/>
-      <c r="AX86" s="101"/>
+      <c r="AX86" s="100"/>
       <c r="BK86" s="8"/>
     </row>
     <row r="87" spans="2:63" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="122"/>
-      <c r="C87" s="110"/>
-      <c r="D87" s="123"/>
-      <c r="E87" s="123"/>
-      <c r="F87" s="123"/>
-      <c r="G87" s="123"/>
-      <c r="H87" s="123"/>
-      <c r="I87" s="123"/>
-      <c r="J87" s="123"/>
-      <c r="K87" s="123"/>
-      <c r="L87" s="123"/>
-      <c r="M87" s="123"/>
-      <c r="N87" s="123"/>
-      <c r="O87" s="123"/>
-      <c r="P87" s="123"/>
-      <c r="Q87" s="123"/>
-      <c r="R87" s="123"/>
-      <c r="S87" s="123"/>
-      <c r="T87" s="123"/>
-      <c r="U87" s="110"/>
-      <c r="V87" s="110"/>
+      <c r="B87" s="121"/>
+      <c r="C87" s="109"/>
+      <c r="D87" s="122"/>
+      <c r="E87" s="122"/>
+      <c r="F87" s="122"/>
+      <c r="G87" s="122"/>
+      <c r="H87" s="122"/>
+      <c r="I87" s="122"/>
+      <c r="J87" s="122"/>
+      <c r="K87" s="122"/>
+      <c r="L87" s="122"/>
+      <c r="M87" s="122"/>
+      <c r="N87" s="122"/>
+      <c r="O87" s="122"/>
+      <c r="P87" s="122"/>
+      <c r="Q87" s="122"/>
+      <c r="R87" s="122"/>
+      <c r="S87" s="122"/>
+      <c r="T87" s="122"/>
+      <c r="U87" s="109"/>
+      <c r="V87" s="109"/>
       <c r="W87" s="63"/>
-      <c r="X87" s="110"/>
-      <c r="Y87" s="110"/>
-      <c r="Z87" s="110"/>
-      <c r="AA87" s="123"/>
-      <c r="AB87" s="110"/>
-      <c r="AC87" s="110"/>
-      <c r="AD87" s="110"/>
-      <c r="AE87" s="110"/>
-      <c r="AF87" s="110"/>
-      <c r="AG87" s="110"/>
-      <c r="AH87" s="110"/>
-      <c r="AI87" s="110"/>
-      <c r="AJ87" s="110"/>
-      <c r="AK87" s="110"/>
-      <c r="AL87" s="110"/>
-      <c r="AM87" s="110"/>
-      <c r="AN87" s="110"/>
+      <c r="X87" s="109"/>
+      <c r="Y87" s="109"/>
+      <c r="Z87" s="109"/>
+      <c r="AA87" s="122"/>
+      <c r="AB87" s="109"/>
+      <c r="AC87" s="109"/>
+      <c r="AD87" s="109"/>
+      <c r="AE87" s="109"/>
+      <c r="AF87" s="109"/>
+      <c r="AG87" s="109"/>
+      <c r="AH87" s="109"/>
+      <c r="AI87" s="109"/>
+      <c r="AJ87" s="109"/>
+      <c r="AK87" s="109"/>
+      <c r="AL87" s="109"/>
+      <c r="AM87" s="109"/>
+      <c r="AN87" s="109"/>
       <c r="AO87" s="11"/>
       <c r="AP87" s="11"/>
-      <c r="AQ87" s="102"/>
-      <c r="AR87" s="103"/>
+      <c r="AQ87" s="101"/>
+      <c r="AR87" s="102"/>
       <c r="AS87" s="11"/>
       <c r="AT87" s="11"/>
       <c r="AU87" s="11"/>
@@ -5706,7 +5673,7 @@
     </row>
     <row r="88" spans="2:63" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="D88" s="48"/>
-      <c r="E88" s="104"/>
+      <c r="E88" s="103"/>
       <c r="F88" s="48"/>
       <c r="G88" s="48"/>
       <c r="H88" s="48"/>
@@ -5727,7 +5694,7 @@
     </row>
     <row r="89" spans="2:63" x14ac:dyDescent="0.25">
       <c r="D89" s="48"/>
-      <c r="E89" s="104"/>
+      <c r="E89" s="103"/>
       <c r="F89" s="48"/>
       <c r="G89" s="48"/>
       <c r="H89" s="48"/>
@@ -5760,12 +5727,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="M2:AO5"/>
-    <mergeCell ref="X12:AO12"/>
-    <mergeCell ref="B8:W8"/>
-    <mergeCell ref="X8:AO8"/>
-    <mergeCell ref="AQ8:BK8"/>
-    <mergeCell ref="X9:AO11"/>
+    <mergeCell ref="BO48:CI48"/>
+    <mergeCell ref="BP59:CF59"/>
+    <mergeCell ref="V62:AO62"/>
+    <mergeCell ref="BO71:CF71"/>
+    <mergeCell ref="B77:BK77"/>
     <mergeCell ref="B78:T78"/>
     <mergeCell ref="B23:BK23"/>
     <mergeCell ref="B40:BK40"/>
@@ -5773,11 +5739,12 @@
     <mergeCell ref="V47:AO47"/>
     <mergeCell ref="AQ47:BK47"/>
     <mergeCell ref="M41:AO44"/>
-    <mergeCell ref="BO48:CI48"/>
-    <mergeCell ref="BP59:CF59"/>
-    <mergeCell ref="V62:AO62"/>
-    <mergeCell ref="BO71:CF71"/>
-    <mergeCell ref="B77:BK77"/>
+    <mergeCell ref="M2:AO5"/>
+    <mergeCell ref="X12:AO12"/>
+    <mergeCell ref="B8:W8"/>
+    <mergeCell ref="X8:AO8"/>
+    <mergeCell ref="AQ8:BK8"/>
+    <mergeCell ref="X9:AO11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="3.937007874015748E-2" footer="0.23622047244094491"/>
